--- a/results/Results.Final.xlsx
+++ b/results/Results.Final.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Results" sheetId="1" state="visible" r:id="rId3"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="833" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="327">
   <si>
     <t xml:space="preserve">Asset ID</t>
   </si>
@@ -201,13 +201,10 @@
     <t xml:space="preserve">Company 6</t>
   </si>
   <si>
-    <t xml:space="preserve">osTicket installer expoed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">osTicket installer exposed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin Dashboard exposed without authentication, can be attacked via No-Direct</t>
+    <t xml:space="preserve">osticket installer exposed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">admin dashboard exposed without authentication, can be attacked via no-direct</t>
   </si>
   <si>
     <t xml:space="preserve">Critical</t>
@@ -219,19 +216,19 @@
     <t xml:space="preserve">New bugs</t>
   </si>
   <si>
-    <t xml:space="preserve">PII exposure on Admin dashboard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Missing HTTP seurity header</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CORS misconfiguration for HTTP to HTTPS redirect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Missing MX, SPF and DMARC records</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSH Password Authentication Enabled on all Three Hosts</t>
+    <t xml:space="preserve">pii exposure on admin dashboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">missing http security headers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cors misconfiguration for http to https redirect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">missing email security records (spf, caa, dmarc, mx)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ssh allows password login</t>
   </si>
   <si>
     <t xml:space="preserve">Medium</t>
@@ -243,22 +240,16 @@
     <t xml:space="preserve">Out-of-scoped</t>
   </si>
   <si>
-    <t xml:space="preserve">Directory Listing on  blog/uploads</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exposed port 8080 via cleartext</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wordpress Directory listing enabled on /wp-content/uploads</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open DNS resolvers for all servers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Missing DMARC and SPF records</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wordpress XML-RPC Enabled</t>
+    <t xml:space="preserve">wordpress directory listing enabled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">apache site exposed on port 8080 via cleartext</t>
+  </si>
+  <si>
+    <t xml:space="preserve">open dns resolvers for all servers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wordpress xml-rpc enabled</t>
   </si>
   <si>
     <t xml:space="preserve">Info</t>
@@ -270,727 +261,631 @@
     <t xml:space="preserve">Out-of-scope</t>
   </si>
   <si>
-    <t xml:space="preserve">Wordpress user enumeration enabled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/api path redirects to HTTP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">osTicket cookie missing security flags</t>
+    <t xml:space="preserve">wordpress user enumeration enabled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/api path redirects to http</t>
+  </si>
+  <si>
+    <t xml:space="preserve">osticket cooke missing security flags</t>
   </si>
   <si>
     <t xml:space="preserve">Out of scope</t>
   </si>
   <si>
-    <t xml:space="preserve">Wordpress Directory Listing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">osTicket cooke missing HttpOnly and SameSite flag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software version and tech disclosure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Directory Listing on /uploads and /wp-includes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PHPSESSID missing baseline security flags</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wordpress XML-RPC has no rate limiting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">osTicket cooke missing HttpOnly flag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contat Form lacks rate limiting and message length validation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contact API experiencing 500 error</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wordpress version disclosure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HTTPS redirect to HTTP on some endpoints</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software version disclosure across three domains</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weak TLS Cipher suite on multiple HTTPS listeners</t>
+    <t xml:space="preserve">server information disclosure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">session cookies missing baseline security flags</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wordpress xml-rpc has no rate limiting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">contat form lacks rate limiting and message length validation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">contact api experiencing 500 error</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wordpress version disclosure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https redirect to http</t>
+  </si>
+  <si>
+    <t xml:space="preserve">weak tls cipher suite on multiple https listeners</t>
   </si>
   <si>
     <t xml:space="preserve">/api/health exposed</t>
   </si>
   <si>
-    <t xml:space="preserve">osTicket web.config file Exposed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSH password authentication exposed on all servers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wordpress REST API routes exposure </t>
-  </si>
-  <si>
-    <t xml:space="preserve">?author=N and wp-links-opml.php endpoints expose Administrator username</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wordpress install and Upgrade endpoints reachable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSH ports exposed with legacy MAC algorithms</t>
+    <t xml:space="preserve">osticket web.config file exposed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wordpress rest api routes exposure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">?author=n and wp-links-opml.php endpoints expose administrator username</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wordpress install and upgrade endpoints reachable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ssh service uses legacy mac algorithms</t>
   </si>
   <si>
     <t xml:space="preserve">honeypot contact form not working</t>
   </si>
   <si>
-    <t xml:space="preserve">Vulnerable Nginx version 1.22.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Advertised info@ausecurity.best cannot receive mail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">osTicket setup endpoint discloses internal server path</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hosting Jurisdiction Mismatch (OVH Singapore vs Sydney Address)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAA, AAAA, robots.txt not published for apex domain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Missing  CAA DNS records</t>
+    <t xml:space="preserve">vulnerable nginx version 1.22.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">advertised info@ausecurity.best cannot receive mail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">osticket setup endpoint discloses internal server path</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hosting jurisdiction mismatch (ovh singapore vs sydney address)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">missing  caa dns records</t>
   </si>
   <si>
     <t xml:space="preserve">Company 1</t>
   </si>
   <si>
-    <t xml:space="preserve">Missing Cookie Secure and sameSite attributes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stored XSS in article Content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TLS Certiicate mismatch on www domain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stored XSS in SVG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flask debug mode enabled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin login does not have rate limiting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSTI in /?q= endpoint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Missing CSRF Protection on admin actions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python application exposed on port 5000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reflected XSS in 404 Handler in /article/&lt;slug&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sensitive Information Disclosure via Unauthenticated API (articles)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Email Spoofing enabled by missing DMARC/DKIM and Softfail SPF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Missing HTTP security headers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cookies missing Secure and SameSite flags</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Session cookies missing Secure and SameSite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin login form with no CSRF token</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Over-exposure of information in /api/search</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JWT access token not revoked after logout</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gunicorn exposed to the internet</t>
+    <t xml:space="preserve">stored xss in article content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tls certiicate mismatch on www domain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stored xss in svg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">flask debug mode enabled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">admin login does not have rate limiting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ssti in /?q= endpoint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mising csrf protection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gunicorn/python application exposed to the internet on port 5000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reflected xss in 404 handler in /article/&lt;slug&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">over-exposure of information in /api/articles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">over-exposure of information in /api/search</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jwt access token not revoked after logout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xss via content-type "text/html"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">over-exposure of information in /api/categories</t>
+  </si>
+  <si>
+    <t xml:space="preserve">business contact is unregistered (thedownundernews.it.com)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">malformed editor account email address</t>
+  </si>
+  <si>
+    <t xml:space="preserve">media subdomain returns 502 bad gateway</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http to https redirect leaks ovh vps hostname</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no cca record for tls certificate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">weak and shared administrator credentials</t>
+  </si>
+  <si>
+    <t xml:space="preserve">contact-form discards all messages</t>
+  </si>
+  <si>
+    <t xml:space="preserve">improper error handling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ssh server offer legacy hma-sha1 message</t>
+  </si>
+  <si>
+    <t xml:space="preserve">directory listing on media.thedownundernews.online</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ssh exposed to public internet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">content-type override for admin login</t>
+  </si>
+  <si>
+    <t xml:space="preserve">company 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">account enumeration via registration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mising  csrf protection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">missing  httponly, secure and samesite flags on cookies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cloudfront uses the wrong tls certificate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">postgresql service exposed to the internet without tls</t>
+  </si>
+  <si>
+    <t xml:space="preserve">idor to change the visibility of a private image</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no rate limiting on login endpoint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">images enumeration via 403 and 404 code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">recursive dns resolver open on public server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">missing hsts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sql errors disclose database and source details</t>
+  </si>
+  <si>
+    <t xml:space="preserve">excessive expiry for pre-signed  urls</t>
+  </si>
+  <si>
+    <t xml:space="preserve">missing content-security-policy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">backend version disclosed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">weak password policy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abusing user_id to inject into aws storage path</t>
+  </si>
+  <si>
+    <t xml:space="preserve">username enumeration via response time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">registration email check is not enforced</t>
+  </si>
+  <si>
+    <t xml:space="preserve">malformed error on empty user_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">client-side cookies store server-consumed state</t>
+  </si>
+  <si>
+    <t xml:space="preserve">weak file-upload validation on /media/upload</t>
+  </si>
+  <si>
+    <t xml:space="preserve">api authentication is functionally unreachable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Company </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iteration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Initial balance (USD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">After balance (USD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost (USD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost (AUD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34m 5s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36m 35s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74m 15s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31m 47s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total (AUD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20m 29s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Error it kept pending when it tried to generate the report. I added 10 dollars so it turned into 9.94 dollars and after the final request, it dropped back to 9.73$.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36m 30s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35m 48s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Opus 4.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43m 38s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27m 55s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67m 34s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claude Opus  4.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56m 45s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46m 53s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64m 18s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63m 21s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24m 28s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90m 28s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117m 45s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62m 12s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39m 2s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38m 43s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124m 19s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40m 29s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38m 46s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35m 18s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50m 25s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">655m 43s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28m 19s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Company ID </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Company name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OVH instance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reason</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1st month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2nd month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Domain name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Domain name price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Price (AUD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Price Final (AUD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DownUnderznews</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vps-8d3f63bd.vps.ovh.ca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Main website</t>
+  </si>
+  <si>
+    <t xml:space="preserve">thedownundernews.online</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vps-edee2c79.vps.ovh.ca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2nd server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">media.thedownundernews.online</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SellNBuy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vps-b4fe231d.vps.ovh.ca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sellandbuy.online</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vps-c8c49001.vps.ovh.ca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User portal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">portal.sellandbuy.online</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Imagur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vps-ad2c3eab.vps.ovh.ca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">main website</t>
+  </si>
+  <si>
+    <t xml:space="preserve">imagesharer.xyz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">treasurysafirm.cyou </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FileShare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vps-05ed378f.vps.ovh.ca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">filesharingservice.shop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AuSecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vps-10f1e4c3.vps.ovh.ca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ausecurity.best</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vps-91287016.vps.ovh.ca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ticket.ausecurity.best, contact.ausecurity.best</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AusSecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vps-d64a720c.vps.ovh.ca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wordpress blog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">blog.ausecurity.best</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Madame Saigon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vps-f8344c71.vps.ovh.ca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">madamesaigon.shop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EdwardClinic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vps-1bccf615.vps.ovh.ca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">edwardclinic.online</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vps-2ae87ea6.vps.ovh.ca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JuiceShop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vps-47037278.vps.ovh.ca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">juiceshopstore.cyou </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SaLaws</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vps-04882f0b.vps.ovh.ca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">salawservice.space</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total hosting price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total domain name price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Domain names (Spaceship)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Domain name cost (USD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Downundernews</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">imagur.online</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SaTreasury</t>
+  </si>
+  <si>
+    <t xml:space="preserve">treasurysa.site</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FileSharer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">filesharer.site </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MadameSaigon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">juiceshop.store</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">salaws.site </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DeepSeek I1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DeepSeek I2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DeepSeek I3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cookie Missing Secure and SameSite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Missing CSRF Protection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stored XSS in article content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Potential Email Spoofing (Missing DMARC, DKIM, SoftFail, SPF)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Informational</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Missing baseline security headers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Disclosure via Unauthenticated API</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gunicorn publicly exposed</t>
   </si>
   <si>
     <t xml:space="preserve">XSS via Content-Type "text/html"</t>
   </si>
   <si>
-    <t xml:space="preserve">HTTP security headers missing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Over-exposure of information in /api/categories</t>
-  </si>
-  <si>
-    <t xml:space="preserve">thedownundernews,it.com not registered</t>
+    <t xml:space="preserve">TLS Certificate mismatch with www</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weak and shared administrator credentials</t>
   </si>
   <si>
     <t xml:space="preserve">Malformed editor account email address</t>
   </si>
   <si>
-    <t xml:space="preserve">Unmoderated public comments with no CSRF protection</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Business contact is unregistered (thedownundernews.it.com)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Media subdomain returns 502 Bad Gateway</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Public-facing SSH allows password authentication</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HTTP to HTTPS redirect leaks OVH VPS Hostname</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Public articles API expose staffs detail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No CCA record for TLS certificate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weak and shared administrator credentials</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contact form never sends a message</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Improper error handling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSH server offer legacy HMA-SHA1 message</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Directory Listing on media.thedownundernews.online</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Over-exposure of information in /api/articles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contact form does not send messages</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSH reachable on the public web server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Content-Type override for admin login</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contact-form discords all messages</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Server Information Disclosure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">company 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Account enumeration via registration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mising  CSRF Protection</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Missing  HttpOnly, Secure and SameSite flags on cookies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloudfront uses the wrong TLS Certificate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Postgres exposed to public internet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IDOR to change the visibility of a private image</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Missing CSRF Protections</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PostgresQL service exposed to the internet without TLS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Apache site exposed on port 8080</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HTTPS redirect to HTTP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No rate limiting on Login endpoint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSH exposed to open internet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Username enumeration via registration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Images enumeration via 403 and 404 code</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recursive DNS resolver open on public server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Missing SPF, DMARC and MX records for emails</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Missing HSTS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQL errors disclose database and source details</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Excessive expiry for pre-signed  URLs </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Missing Content-Security-Policy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Backend version disclosed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weak password policy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Abusing user_id to inject into AWS storage path</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSH allows password login</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Postgres reachable on the internet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Username enumeration via response time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Registration email check is not enforced</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSH service exposed on public VPS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Malformed error on empty user_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">s</t>
-  </si>
-  <si>
-    <t xml:space="preserve">www hostname certificate mismatch </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Client-side cookies store server-consumed state</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSH Exposed to public internet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weak file-upload validation on /media/upload</t>
-  </si>
-  <si>
-    <t xml:space="preserve">API authentication is functionally unreachable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Company </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Iteration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Model</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Initial balance (USD)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">After balance (USD)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cost (USD)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cost (AUD)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34m 5s</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36m 35s</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74m 15s</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31m 47s</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total (AUD)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20m 29s</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Error it kept pending when it tried to generate the report. I added 10 dollars so it turned into 9.94 dollars and after the final request, it dropped back to 9.73$.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Average</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36m 30s</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35m 48s</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Opus 4.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43m 38s</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27m 55s</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67m 34s</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claude Opus  4.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56m 45s</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46m 53s</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64m 18s</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63m 21s</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24m 28s</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90m 28s</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117m 45s</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62m 12s</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39m 2s</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38m 43s</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124m 19s</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40m 29s</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38m 46s</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35m 18s</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50m 25s</t>
-  </si>
-  <si>
-    <t xml:space="preserve">655m 43s</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28m 19s</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Company ID </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Company name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OVH instance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reason</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1st month</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2nd month</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Domain name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Domain name price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Price (AUD)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Price Final (AUD)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DownUnderznews</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vps-8d3f63bd.vps.ovh.ca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Main website</t>
-  </si>
-  <si>
-    <t xml:space="preserve">thedownundernews.online</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vps-edee2c79.vps.ovh.ca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2nd server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">media.thedownundernews.online</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SellNBuy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vps-b4fe231d.vps.ovh.ca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sellandbuy.online</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vps-c8c49001.vps.ovh.ca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">User portal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">portal.sellandbuy.online</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Imagur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vps-ad2c3eab.vps.ovh.ca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">main website</t>
-  </si>
-  <si>
-    <t xml:space="preserve">imagesharer.xyz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">X</t>
-  </si>
-  <si>
-    <t xml:space="preserve">treasurysafirm.cyou </t>
-  </si>
-  <si>
-    <t xml:space="preserve">FileShare</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vps-05ed378f.vps.ovh.ca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">filesharingservice.shop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AuSecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vps-10f1e4c3.vps.ovh.ca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ausecurity.best</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vps-91287016.vps.ovh.ca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ticket.ausecurity.best, contact.ausecurity.best</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AusSecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vps-d64a720c.vps.ovh.ca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wordpress blog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">blog.ausecurity.best</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Madame Saigon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vps-f8344c71.vps.ovh.ca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">madamesaigon.shop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EdwardClinic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vps-1bccf615.vps.ovh.ca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">edwardclinic.online</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vps-2ae87ea6.vps.ovh.ca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JuiceShop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vps-47037278.vps.ovh.ca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">juiceshopstore.cyou </t>
-  </si>
-  <si>
-    <t xml:space="preserve">SaLaws</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vps-04882f0b.vps.ovh.ca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">salawservice.space</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total hosting price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total domain name price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Domain names (Spaceship)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Domain name cost (USD)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Downundernews</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">imagur.online</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SaTreasury</t>
-  </si>
-  <si>
-    <t xml:space="preserve">treasurysa.site</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FileSharer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">filesharer.site </t>
-  </si>
-  <si>
-    <t xml:space="preserve">C6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MadameSaigon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">juiceshop.store</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">salaws.site </t>
-  </si>
-  <si>
-    <t xml:space="preserve">DeepSeek I1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DeepSeek I2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DeepSeek I3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cookie Missing Secure and SameSite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Missing CSRF Protection</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stored XSS in article content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Potential Email Spoofing (Missing DMARC, DKIM, SoftFail, SPF)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Informational</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Missing baseline security headers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Disclosure via Unauthenticated API</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gunicorn publicly exposed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TLS Certificate mismatch with www</t>
   </si>
   <si>
     <t xml:space="preserve">Company</t>
@@ -1134,7 +1029,7 @@
     <numFmt numFmtId="166" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
     <numFmt numFmtId="167" formatCode="0.00"/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="33">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1248,6 +1143,13 @@
       <color rgb="FF595959"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -1710,780 +1612,788 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="194">
+  <cellXfs count="196">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="7" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="7" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="7" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="7" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="8" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="8" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="9" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="9" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="9" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="9" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="7" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="7" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="10" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="10" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="11" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="11" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="9" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="9" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="19" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="19" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="21" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="21" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="19" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="19" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="19" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="19" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="9" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="9" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="22" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="22" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="22" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="22" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="23" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="23" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="22" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="22" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="11" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="11" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="10" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="10" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="10" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="10" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="13" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="13" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="12" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="12" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="15" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="15" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="17" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="15" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="15" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="15" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="15" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="15" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="15" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="16" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="16" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="17" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="17" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="16" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="16" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="17" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="17" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="17" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="17" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="17" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="17" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="17" fillId="17" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="16" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="12" fillId="16" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="14" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="17" fillId="15" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="17" fillId="14" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="18" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="19" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="22" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="22" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="20" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="18" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="25" fillId="19" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="9" borderId="22" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="22" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="9" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="20" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="30" fillId="0" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="30" fillId="0" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="31" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="31" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="30" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2799,11 +2709,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="66496591"/>
-        <c:axId val="79572304"/>
+        <c:axId val="1016164"/>
+        <c:axId val="85484299"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="66496591"/>
+        <c:axId val="1016164"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2842,7 +2752,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="79572304"/>
+        <c:crossAx val="85484299"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2850,7 +2760,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="79572304"/>
+        <c:axId val="85484299"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2896,7 +2806,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="66496591"/>
+        <c:crossAx val="1016164"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3268,11 +3178,11 @@
         </c:ser>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="20576399"/>
-        <c:axId val="31797490"/>
+        <c:axId val="46346045"/>
+        <c:axId val="17785831"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="20576399"/>
+        <c:axId val="46346045"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3311,7 +3221,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="31797490"/>
+        <c:crossAx val="17785831"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3319,7 +3229,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="31797490"/>
+        <c:axId val="17785831"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3365,7 +3275,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="20576399"/>
+        <c:crossAx val="46346045"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3724,11 +3634,11 @@
         </c:ser>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="12299626"/>
-        <c:axId val="15351843"/>
+        <c:axId val="74569294"/>
+        <c:axId val="10011181"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="12299626"/>
+        <c:axId val="74569294"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3767,7 +3677,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="15351843"/>
+        <c:crossAx val="10011181"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3775,7 +3685,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="15351843"/>
+        <c:axId val="10011181"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3821,7 +3731,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="12299626"/>
+        <c:crossAx val="74569294"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4193,11 +4103,11 @@
         </c:ser>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="10270280"/>
-        <c:axId val="31167712"/>
+        <c:axId val="43747546"/>
+        <c:axId val="31302255"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="10270280"/>
+        <c:axId val="43747546"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4236,7 +4146,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="31167712"/>
+        <c:crossAx val="31302255"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4244,7 +4154,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="31167712"/>
+        <c:axId val="31302255"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4290,7 +4200,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="10270280"/>
+        <c:crossAx val="43747546"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4494,11 +4404,11 @@
         </c:ser>
         <c:gapWidth val="182"/>
         <c:overlap val="0"/>
-        <c:axId val="28773236"/>
-        <c:axId val="52187589"/>
+        <c:axId val="26909158"/>
+        <c:axId val="58492580"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="28773236"/>
+        <c:axId val="26909158"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4537,7 +4447,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="52187589"/>
+        <c:crossAx val="58492580"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4545,7 +4455,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="52187589"/>
+        <c:axId val="58492580"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -4593,7 +4503,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="28773236"/>
+        <c:crossAx val="26909158"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="0.5"/>
@@ -4680,11 +4590,9 @@
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="419">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
-    <cs:lineWidthScale>1</cs:lineWidthScale>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-    <a:defRPr sz="1800" b="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
   </cs:axisTitle>
   <cs:categoryAxis>
     <cs:lnRef idx="0"/>
@@ -4892,11 +4800,9 @@
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="419">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
-    <cs:lineWidthScale>1</cs:lineWidthScale>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-    <a:defRPr sz="1800" b="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
   </cs:axisTitle>
   <cs:categoryAxis>
     <cs:lnRef idx="0"/>
@@ -5104,11 +5010,9 @@
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="419">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
-    <cs:lineWidthScale>1</cs:lineWidthScale>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-    <a:defRPr sz="1800" b="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
   </cs:axisTitle>
   <cs:categoryAxis>
     <cs:lnRef idx="0"/>
@@ -5316,11 +5220,9 @@
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="419">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
-    <cs:lineWidthScale>1</cs:lineWidthScale>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-    <a:defRPr sz="1800" b="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
   </cs:axisTitle>
   <cs:categoryAxis>
     <cs:lnRef idx="0"/>
@@ -5528,11 +5430,9 @@
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="419">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
-    <cs:lineWidthScale>1</cs:lineWidthScale>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-    <a:defRPr sz="1800" b="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
   </cs:axisTitle>
   <cs:categoryAxis>
     <cs:lnRef idx="0"/>
@@ -5747,9 +5647,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>747000</xdr:colOff>
+      <xdr:colOff>745920</xdr:colOff>
       <xdr:row>30</xdr:row>
-      <xdr:rowOff>3960</xdr:rowOff>
+      <xdr:rowOff>2880</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -5758,7 +5658,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="23545440" y="1724040"/>
-        <a:ext cx="8037720" cy="5481000"/>
+        <a:ext cx="8036640" cy="5479920"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -5782,9 +5682,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>26</xdr:col>
-      <xdr:colOff>357120</xdr:colOff>
+      <xdr:colOff>356040</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>135000</xdr:rowOff>
+      <xdr:rowOff>133920</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -5793,7 +5693,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="39996360" y="3737160"/>
-        <a:ext cx="15008760" cy="4322520"/>
+        <a:ext cx="15007680" cy="4321440"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -5812,9 +5712,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>26</xdr:col>
-      <xdr:colOff>269640</xdr:colOff>
+      <xdr:colOff>268560</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>493920</xdr:rowOff>
+      <xdr:rowOff>492840</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -5823,7 +5723,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="39944880" y="1499040"/>
-        <a:ext cx="14972760" cy="1919160"/>
+        <a:ext cx="14971680" cy="1918080"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -5842,9 +5742,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>29</xdr:col>
-      <xdr:colOff>32400</xdr:colOff>
+      <xdr:colOff>31320</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>247680</xdr:rowOff>
+      <xdr:rowOff>246600</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -5853,7 +5753,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="38044800" y="8863560"/>
-        <a:ext cx="22941360" cy="1947240"/>
+        <a:ext cx="22940280" cy="1946160"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -5877,9 +5777,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>75240</xdr:colOff>
+      <xdr:colOff>74160</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>103680</xdr:rowOff>
+      <xdr:rowOff>102600</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -5888,7 +5788,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="8493480" y="274680"/>
-        <a:ext cx="5349960" cy="3115080"/>
+        <a:ext cx="5348880" cy="3114000"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -7437,31 +7337,31 @@
         <v>58</v>
       </c>
       <c r="E3" s="90" t="s">
+        <v>58</v>
+      </c>
+      <c r="F3" s="90" t="s">
+        <v>58</v>
+      </c>
+      <c r="G3" s="91" t="s">
         <v>59</v>
       </c>
-      <c r="F3" s="90" t="s">
-        <v>59</v>
-      </c>
-      <c r="G3" s="91" t="s">
+      <c r="H3" s="90" t="s">
+        <v>58</v>
+      </c>
+      <c r="I3" s="90" t="s">
+        <v>58</v>
+      </c>
+      <c r="J3" s="90" t="s">
+        <v>58</v>
+      </c>
+      <c r="M3" s="92" t="s">
         <v>60</v>
       </c>
-      <c r="H3" s="90" t="s">
-        <v>59</v>
-      </c>
-      <c r="I3" s="90" t="s">
-        <v>59</v>
-      </c>
-      <c r="J3" s="90" t="s">
-        <v>59</v>
-      </c>
-      <c r="M3" s="92" t="s">
+      <c r="N3" s="93" t="s">
         <v>61</v>
       </c>
-      <c r="N3" s="93" t="s">
+      <c r="AE3" s="88" t="s">
         <v>62</v>
-      </c>
-      <c r="AE3" s="88" t="s">
-        <v>63</v>
       </c>
       <c r="AF3" s="2" t="n">
         <v>7</v>
@@ -7482,40 +7382,40 @@
     <row r="4" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="89"/>
       <c r="B4" s="91" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4" s="91" t="s">
+        <v>59</v>
+      </c>
+      <c r="D4" s="94" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" s="95" t="s">
         <v>64</v>
       </c>
-      <c r="C4" s="91" t="s">
-        <v>60</v>
-      </c>
-      <c r="D4" s="94" t="s">
-        <v>60</v>
-      </c>
-      <c r="E4" s="95" t="s">
+      <c r="F4" s="95" t="s">
         <v>65</v>
       </c>
-      <c r="F4" s="95" t="s">
+      <c r="G4" s="95" t="s">
+        <v>64</v>
+      </c>
+      <c r="H4" s="91" t="s">
         <v>66</v>
       </c>
-      <c r="G4" s="95" t="s">
-        <v>65</v>
-      </c>
-      <c r="H4" s="91" t="s">
+      <c r="I4" s="91" t="s">
+        <v>66</v>
+      </c>
+      <c r="J4" s="96" t="s">
         <v>67</v>
       </c>
-      <c r="I4" s="91" t="s">
-        <v>67</v>
-      </c>
-      <c r="J4" s="96" t="s">
+      <c r="M4" s="97" t="s">
         <v>68</v>
       </c>
-      <c r="M4" s="97" t="s">
+      <c r="N4" s="98" t="s">
         <v>69</v>
       </c>
-      <c r="N4" s="98" t="s">
+      <c r="AE4" s="99" t="s">
         <v>70</v>
-      </c>
-      <c r="AE4" s="99" t="s">
-        <v>71</v>
       </c>
       <c r="AF4" s="2" t="n">
         <v>0</v>
@@ -7536,79 +7436,79 @@
     <row r="5" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="89"/>
       <c r="B5" s="100" t="s">
+        <v>71</v>
+      </c>
+      <c r="C5" s="101" t="s">
         <v>72</v>
       </c>
-      <c r="C5" s="101" t="s">
+      <c r="D5" s="102" t="s">
+        <v>71</v>
+      </c>
+      <c r="E5" s="95" t="s">
+        <v>66</v>
+      </c>
+      <c r="F5" s="103" t="s">
         <v>73</v>
       </c>
-      <c r="D5" s="102" t="s">
+      <c r="G5" s="95" t="s">
+        <v>66</v>
+      </c>
+      <c r="H5" s="91" t="s">
         <v>74</v>
       </c>
-      <c r="E5" s="95" t="s">
-        <v>67</v>
-      </c>
-      <c r="F5" s="103" t="s">
+      <c r="I5" s="91" t="s">
+        <v>72</v>
+      </c>
+      <c r="J5" s="91" t="s">
+        <v>72</v>
+      </c>
+      <c r="M5" s="104" t="s">
         <v>75</v>
       </c>
-      <c r="G5" s="95" t="s">
+      <c r="N5" s="105" t="s">
         <v>76</v>
       </c>
-      <c r="H5" s="91" t="s">
+      <c r="AF5" s="106" t="s">
+        <v>76</v>
+      </c>
+      <c r="AG5" s="106" t="s">
+        <v>62</v>
+      </c>
+      <c r="AH5" s="106" t="s">
         <v>77</v>
-      </c>
-      <c r="I5" s="91" t="s">
-        <v>73</v>
-      </c>
-      <c r="J5" s="91" t="s">
-        <v>73</v>
-      </c>
-      <c r="M5" s="104" t="s">
-        <v>78</v>
-      </c>
-      <c r="N5" s="105" t="s">
-        <v>79</v>
-      </c>
-      <c r="AF5" s="106" t="s">
-        <v>79</v>
-      </c>
-      <c r="AG5" s="106" t="s">
-        <v>63</v>
-      </c>
-      <c r="AH5" s="106" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="89"/>
       <c r="B6" s="100" t="s">
+        <v>78</v>
+      </c>
+      <c r="C6" s="95" t="s">
+        <v>64</v>
+      </c>
+      <c r="D6" s="102" t="s">
+        <v>64</v>
+      </c>
+      <c r="E6" s="95" t="s">
+        <v>74</v>
+      </c>
+      <c r="F6" s="95" t="s">
+        <v>74</v>
+      </c>
+      <c r="G6" s="95" t="s">
+        <v>79</v>
+      </c>
+      <c r="H6" s="101" t="s">
+        <v>80</v>
+      </c>
+      <c r="I6" s="107" t="s">
+        <v>63</v>
+      </c>
+      <c r="J6" s="107" t="s">
+        <v>66</v>
+      </c>
+      <c r="M6" s="51" t="s">
         <v>81</v>
-      </c>
-      <c r="C6" s="95" t="s">
-        <v>65</v>
-      </c>
-      <c r="D6" s="102" t="s">
-        <v>65</v>
-      </c>
-      <c r="E6" s="95" t="s">
-        <v>77</v>
-      </c>
-      <c r="F6" s="95" t="s">
-        <v>77</v>
-      </c>
-      <c r="G6" s="95" t="s">
-        <v>82</v>
-      </c>
-      <c r="H6" s="101" t="s">
-        <v>83</v>
-      </c>
-      <c r="I6" s="96" t="s">
-        <v>64</v>
-      </c>
-      <c r="J6" s="96" t="s">
-        <v>67</v>
-      </c>
-      <c r="M6" s="51" t="s">
-        <v>84</v>
       </c>
       <c r="AE6" s="81" t="s">
         <v>18</v>
@@ -7626,31 +7526,31 @@
     <row r="7" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="89"/>
       <c r="B7" s="100" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C7" s="100" t="s">
-        <v>85</v>
-      </c>
-      <c r="D7" s="107" t="s">
-        <v>81</v>
+        <v>71</v>
+      </c>
+      <c r="D7" s="108" t="s">
+        <v>78</v>
       </c>
       <c r="E7" s="95" t="s">
+        <v>63</v>
+      </c>
+      <c r="F7" s="100" t="s">
+        <v>80</v>
+      </c>
+      <c r="G7" s="109" t="s">
+        <v>82</v>
+      </c>
+      <c r="H7" s="101" t="s">
         <v>64</v>
       </c>
-      <c r="F7" s="100" t="s">
-        <v>86</v>
-      </c>
-      <c r="G7" s="108" t="s">
-        <v>87</v>
-      </c>
-      <c r="H7" s="101" t="s">
-        <v>65</v>
-      </c>
       <c r="I7" s="91" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="J7" s="91" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="AE7" s="32" t="s">
         <v>20</v>
@@ -7668,29 +7568,29 @@
     <row r="8" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="89"/>
       <c r="B8" s="100" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C8" s="101" t="s">
-        <v>81</v>
-      </c>
-      <c r="D8" s="107" t="s">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="D8" s="108" t="s">
+        <v>74</v>
       </c>
       <c r="E8" s="95" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="F8" s="95" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="G8" s="77"/>
       <c r="H8" s="101" t="s">
-        <v>73</v>
-      </c>
-      <c r="I8" s="96" t="s">
-        <v>89</v>
+        <v>72</v>
+      </c>
+      <c r="I8" s="107" t="s">
+        <v>83</v>
       </c>
       <c r="J8" s="95" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="AE8" s="83" t="s">
         <v>22</v>
@@ -7707,124 +7607,124 @@
     </row>
     <row r="9" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="89"/>
-      <c r="B9" s="109" t="s">
-        <v>87</v>
+      <c r="B9" s="110" t="s">
+        <v>82</v>
       </c>
       <c r="C9" s="100" t="s">
-        <v>91</v>
-      </c>
-      <c r="D9" s="109" t="s">
-        <v>87</v>
+        <v>80</v>
+      </c>
+      <c r="D9" s="110" t="s">
+        <v>82</v>
       </c>
       <c r="E9" s="95" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F9" s="95" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G9" s="77"/>
       <c r="H9" s="101" t="s">
+        <v>71</v>
+      </c>
+      <c r="I9" s="95" t="s">
         <v>85</v>
       </c>
-      <c r="I9" s="95" t="s">
-        <v>92</v>
-      </c>
       <c r="J9" s="95" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="89"/>
-      <c r="B10" s="110"/>
-      <c r="C10" s="111" t="s">
-        <v>93</v>
-      </c>
-      <c r="D10" s="108" t="s">
-        <v>94</v>
+      <c r="B10" s="111"/>
+      <c r="C10" s="112" t="s">
+        <v>86</v>
+      </c>
+      <c r="D10" s="109" t="s">
+        <v>87</v>
       </c>
       <c r="E10" s="95" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="F10" s="95" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G10" s="77"/>
       <c r="H10" s="101" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="I10" s="95" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J10" s="95" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="89"/>
-      <c r="B11" s="110"/>
-      <c r="C11" s="109" t="s">
-        <v>87</v>
+      <c r="B11" s="111"/>
+      <c r="C11" s="110" t="s">
+        <v>82</v>
       </c>
       <c r="D11" s="77"/>
-      <c r="E11" s="108" t="s">
-        <v>96</v>
+      <c r="E11" s="109" t="s">
+        <v>82</v>
       </c>
       <c r="F11" s="95" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G11" s="77"/>
-      <c r="H11" s="107" t="s">
-        <v>97</v>
+      <c r="H11" s="108" t="s">
+        <v>89</v>
       </c>
       <c r="I11" s="95" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="J11" s="95" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="89"/>
-      <c r="B12" s="110"/>
-      <c r="C12" s="112" t="s">
-        <v>77</v>
+      <c r="B12" s="111"/>
+      <c r="C12" s="113" t="s">
+        <v>74</v>
       </c>
       <c r="D12" s="77"/>
       <c r="E12" s="77"/>
-      <c r="F12" s="108" t="s">
-        <v>100</v>
+      <c r="F12" s="114" t="s">
+        <v>67</v>
       </c>
       <c r="G12" s="77"/>
-      <c r="H12" s="112" t="s">
-        <v>101</v>
+      <c r="H12" s="113" t="s">
+        <v>92</v>
       </c>
       <c r="I12" s="95" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="J12" s="101" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="89"/>
-      <c r="B13" s="110"/>
-      <c r="C13" s="109" t="s">
-        <v>94</v>
+      <c r="B13" s="111"/>
+      <c r="C13" s="110" t="s">
+        <v>87</v>
       </c>
       <c r="D13" s="77"/>
       <c r="E13" s="77"/>
-      <c r="F13" s="108" t="s">
+      <c r="F13" s="109" t="s">
+        <v>82</v>
+      </c>
+      <c r="G13" s="77"/>
+      <c r="H13" s="113" t="s">
         <v>87</v>
       </c>
-      <c r="G13" s="77"/>
-      <c r="H13" s="112" t="s">
+      <c r="I13" s="101" t="s">
+        <v>78</v>
+      </c>
+      <c r="J13" s="95" t="s">
         <v>94</v>
-      </c>
-      <c r="I13" s="101" t="s">
-        <v>81</v>
-      </c>
-      <c r="J13" s="95" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7833,18 +7733,18 @@
       <c r="C14" s="77"/>
       <c r="D14" s="77"/>
       <c r="E14" s="77"/>
-      <c r="F14" s="112" t="s">
-        <v>60</v>
+      <c r="F14" s="113" t="s">
+        <v>59</v>
       </c>
       <c r="G14" s="77"/>
       <c r="H14" s="101" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="I14" s="101" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="J14" s="95" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7856,13 +7756,13 @@
       <c r="F15" s="77"/>
       <c r="G15" s="77"/>
       <c r="H15" s="103" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="I15" s="95" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="J15" s="95" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7873,12 +7773,12 @@
       <c r="E16" s="77"/>
       <c r="F16" s="77"/>
       <c r="G16" s="77"/>
-      <c r="H16" s="113"/>
-      <c r="I16" s="114" t="s">
-        <v>107</v>
+      <c r="H16" s="115"/>
+      <c r="I16" s="116" t="s">
+        <v>98</v>
       </c>
       <c r="J16" s="95" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7889,12 +7789,12 @@
       <c r="E17" s="77"/>
       <c r="F17" s="77"/>
       <c r="G17" s="77"/>
-      <c r="H17" s="113"/>
-      <c r="I17" s="115" t="s">
-        <v>109</v>
+      <c r="H17" s="115"/>
+      <c r="I17" s="117" t="s">
+        <v>100</v>
       </c>
       <c r="J17" s="95" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7907,10 +7807,10 @@
       <c r="G18" s="77"/>
       <c r="H18" s="77"/>
       <c r="I18" s="104" t="s">
-        <v>110</v>
-      </c>
-      <c r="J18" s="116" t="s">
-        <v>111</v>
+        <v>66</v>
+      </c>
+      <c r="J18" s="118" t="s">
+        <v>101</v>
       </c>
       <c r="AF18" s="81" t="s">
         <v>18</v>
@@ -7930,34 +7830,34 @@
     </row>
     <row r="19" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="89" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="B19" s="95" t="s">
-        <v>113</v>
-      </c>
-      <c r="C19" s="96" t="s">
-        <v>114</v>
-      </c>
-      <c r="D19" s="96" t="s">
-        <v>114</v>
+        <v>83</v>
+      </c>
+      <c r="C19" s="107" t="s">
+        <v>103</v>
+      </c>
+      <c r="D19" s="107" t="s">
+        <v>103</v>
       </c>
       <c r="E19" s="95" t="s">
-        <v>115</v>
-      </c>
-      <c r="F19" s="96" t="s">
-        <v>116</v>
-      </c>
-      <c r="G19" s="96" t="s">
-        <v>117</v>
-      </c>
-      <c r="H19" s="117" t="s">
-        <v>118</v>
-      </c>
-      <c r="I19" s="118" t="s">
-        <v>119</v>
-      </c>
-      <c r="J19" s="96" t="s">
-        <v>114</v>
+        <v>104</v>
+      </c>
+      <c r="F19" s="107" t="s">
+        <v>105</v>
+      </c>
+      <c r="G19" s="107" t="s">
+        <v>106</v>
+      </c>
+      <c r="H19" s="119" t="s">
+        <v>107</v>
+      </c>
+      <c r="I19" s="120" t="s">
+        <v>108</v>
+      </c>
+      <c r="J19" s="107" t="s">
+        <v>103</v>
       </c>
       <c r="AE19" s="88" t="s">
         <v>56</v>
@@ -7981,34 +7881,34 @@
     <row r="20" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="89"/>
       <c r="B20" s="95" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="C20" s="95" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="D20" s="95" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="E20" s="95" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="F20" s="95" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="G20" s="95" t="s">
-        <v>121</v>
-      </c>
-      <c r="H20" s="96" t="s">
-        <v>123</v>
-      </c>
-      <c r="I20" s="96" t="s">
-        <v>114</v>
-      </c>
-      <c r="J20" s="96" t="s">
-        <v>116</v>
+        <v>110</v>
+      </c>
+      <c r="H20" s="107" t="s">
+        <v>112</v>
+      </c>
+      <c r="I20" s="107" t="s">
+        <v>103</v>
+      </c>
+      <c r="J20" s="107" t="s">
+        <v>105</v>
       </c>
       <c r="AE20" s="88" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AF20" s="2" t="n">
         <v>7</v>
@@ -8028,35 +7928,35 @@
     </row>
     <row r="21" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="89"/>
-      <c r="B21" s="108" t="s">
-        <v>124</v>
-      </c>
-      <c r="C21" s="116" t="s">
-        <v>125</v>
+      <c r="B21" s="109" t="s">
+        <v>66</v>
+      </c>
+      <c r="C21" s="118" t="s">
+        <v>64</v>
       </c>
       <c r="D21" s="95" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="E21" s="95" t="s">
-        <v>126</v>
+        <v>83</v>
       </c>
       <c r="F21" s="95" t="s">
-        <v>127</v>
+        <v>83</v>
       </c>
       <c r="G21" s="95" t="s">
-        <v>128</v>
-      </c>
-      <c r="H21" s="96" t="s">
-        <v>129</v>
+        <v>109</v>
+      </c>
+      <c r="H21" s="107" t="s">
+        <v>113</v>
       </c>
       <c r="I21" s="95" t="s">
-        <v>118</v>
-      </c>
-      <c r="J21" s="96" t="s">
-        <v>130</v>
+        <v>107</v>
+      </c>
+      <c r="J21" s="107" t="s">
+        <v>114</v>
       </c>
       <c r="AE21" s="99" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AF21" s="2" t="n">
         <v>2</v>
@@ -8076,69 +7976,69 @@
     </row>
     <row r="22" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="89"/>
-      <c r="B22" s="108" t="s">
-        <v>131</v>
-      </c>
-      <c r="C22" s="116" t="s">
-        <v>126</v>
+      <c r="B22" s="109" t="s">
+        <v>110</v>
+      </c>
+      <c r="C22" s="118" t="s">
+        <v>83</v>
       </c>
       <c r="D22" s="95" t="s">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="E22" s="95" t="s">
-        <v>133</v>
+        <v>64</v>
       </c>
       <c r="F22" s="95" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="G22" s="95" t="s">
-        <v>127</v>
-      </c>
-      <c r="H22" s="96" t="s">
-        <v>134</v>
-      </c>
-      <c r="I22" s="119" t="s">
-        <v>135</v>
-      </c>
-      <c r="J22" s="96" t="s">
-        <v>127</v>
+        <v>83</v>
+      </c>
+      <c r="H22" s="107" t="s">
+        <v>116</v>
+      </c>
+      <c r="I22" s="121" t="s">
+        <v>117</v>
+      </c>
+      <c r="J22" s="107" t="s">
+        <v>83</v>
       </c>
       <c r="AF22" s="106" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="AG22" s="106" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AH22" s="106" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="89"/>
       <c r="B23" s="103" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="C23" s="77"/>
-      <c r="D23" s="116" t="s">
-        <v>126</v>
+      <c r="D23" s="118" t="s">
+        <v>83</v>
       </c>
       <c r="E23" s="95" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="F23" s="95" t="s">
-        <v>137</v>
+        <v>109</v>
       </c>
       <c r="G23" s="95" t="s">
-        <v>125</v>
-      </c>
-      <c r="H23" s="96" t="s">
-        <v>121</v>
+        <v>64</v>
+      </c>
+      <c r="H23" s="107" t="s">
+        <v>110</v>
       </c>
       <c r="I23" s="95" t="s">
-        <v>125</v>
-      </c>
-      <c r="J23" s="119" t="s">
-        <v>138</v>
+        <v>64</v>
+      </c>
+      <c r="J23" s="121" t="s">
+        <v>117</v>
       </c>
       <c r="AE23" s="81" t="s">
         <v>18</v>
@@ -8155,30 +8055,30 @@
     </row>
     <row r="24" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="89"/>
-      <c r="B24" s="119" t="s">
-        <v>139</v>
+      <c r="B24" s="121" t="s">
+        <v>119</v>
       </c>
       <c r="C24" s="77"/>
-      <c r="D24" s="116" t="s">
-        <v>125</v>
-      </c>
-      <c r="E24" s="95" t="s">
-        <v>140</v>
+      <c r="D24" s="118" t="s">
+        <v>64</v>
+      </c>
+      <c r="E24" s="122" t="s">
+        <v>67</v>
       </c>
       <c r="F24" s="95" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="G24" s="95" t="s">
-        <v>124</v>
-      </c>
-      <c r="H24" s="96" t="s">
-        <v>137</v>
+        <v>66</v>
+      </c>
+      <c r="H24" s="107" t="s">
+        <v>109</v>
       </c>
       <c r="I24" s="95" t="s">
-        <v>141</v>
+        <v>120</v>
       </c>
       <c r="J24" s="95" t="s">
-        <v>125</v>
+        <v>64</v>
       </c>
       <c r="AE24" s="32" t="s">
         <v>20</v>
@@ -8195,28 +8095,28 @@
     </row>
     <row r="25" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="89"/>
-      <c r="B25" s="108" t="s">
-        <v>125</v>
+      <c r="B25" s="109" t="s">
+        <v>64</v>
       </c>
       <c r="C25" s="77"/>
-      <c r="D25" s="108" t="s">
-        <v>115</v>
+      <c r="D25" s="109" t="s">
+        <v>104</v>
       </c>
       <c r="E25" s="77"/>
       <c r="F25" s="95" t="s">
-        <v>133</v>
+        <v>64</v>
       </c>
       <c r="G25" s="95" t="s">
-        <v>142</v>
+        <v>112</v>
       </c>
       <c r="H25" s="95" t="s">
-        <v>143</v>
+        <v>121</v>
       </c>
       <c r="I25" s="95" t="s">
-        <v>127</v>
+        <v>83</v>
       </c>
       <c r="J25" s="95" t="s">
-        <v>124</v>
+        <v>66</v>
       </c>
       <c r="AE25" s="83" t="s">
         <v>22</v>
@@ -8233,49 +8133,49 @@
     </row>
     <row r="26" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="89"/>
-      <c r="B26" s="108" t="s">
-        <v>115</v>
+      <c r="B26" s="109" t="s">
+        <v>104</v>
       </c>
       <c r="C26" s="77"/>
-      <c r="D26" s="116" t="s">
-        <v>144</v>
+      <c r="D26" s="118" t="s">
+        <v>122</v>
       </c>
       <c r="E26" s="77"/>
-      <c r="F26" s="108" t="s">
-        <v>145</v>
+      <c r="F26" s="109" t="s">
+        <v>123</v>
       </c>
       <c r="G26" s="95" t="s">
-        <v>137</v>
+        <v>109</v>
       </c>
       <c r="H26" s="95" t="s">
-        <v>146</v>
-      </c>
-      <c r="I26" s="116" t="s">
-        <v>147</v>
+        <v>124</v>
+      </c>
+      <c r="I26" s="118" t="s">
+        <v>125</v>
       </c>
       <c r="J26" s="95" t="s">
-        <v>148</v>
+        <v>126</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="89"/>
-      <c r="B27" s="108" t="s">
-        <v>149</v>
+      <c r="B27" s="109" t="s">
+        <v>112</v>
       </c>
       <c r="C27" s="77"/>
       <c r="D27" s="77"/>
       <c r="E27" s="77"/>
-      <c r="F27" s="108" t="s">
-        <v>146</v>
+      <c r="F27" s="109" t="s">
+        <v>124</v>
       </c>
       <c r="G27" s="95" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="H27" s="95" t="s">
-        <v>125</v>
-      </c>
-      <c r="I27" s="116" t="s">
-        <v>124</v>
+        <v>64</v>
+      </c>
+      <c r="I27" s="118" t="s">
+        <v>66</v>
       </c>
       <c r="J27" s="77"/>
     </row>
@@ -8286,11 +8186,11 @@
       <c r="D28" s="77"/>
       <c r="E28" s="77"/>
       <c r="F28" s="77"/>
-      <c r="G28" s="119" t="s">
-        <v>150</v>
+      <c r="G28" s="121" t="s">
+        <v>123</v>
       </c>
       <c r="H28" s="95" t="s">
-        <v>127</v>
+        <v>83</v>
       </c>
       <c r="I28" s="77"/>
       <c r="J28" s="77"/>
@@ -8302,11 +8202,11 @@
       <c r="D29" s="77"/>
       <c r="E29" s="77"/>
       <c r="F29" s="77"/>
-      <c r="G29" s="108" t="s">
-        <v>151</v>
+      <c r="G29" s="109" t="s">
+        <v>127</v>
       </c>
       <c r="H29" s="95" t="s">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="I29" s="77"/>
       <c r="J29" s="77"/>
@@ -8320,7 +8220,7 @@
       <c r="F30" s="77"/>
       <c r="G30" s="77"/>
       <c r="H30" s="95" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="I30" s="77"/>
       <c r="J30" s="77"/>
@@ -8333,8 +8233,8 @@
       <c r="E31" s="77"/>
       <c r="F31" s="77"/>
       <c r="G31" s="77"/>
-      <c r="H31" s="108" t="s">
-        <v>152</v>
+      <c r="H31" s="109" t="s">
+        <v>128</v>
       </c>
       <c r="I31" s="77"/>
       <c r="J31" s="77"/>
@@ -8347,8 +8247,8 @@
       <c r="E32" s="77"/>
       <c r="F32" s="77"/>
       <c r="G32" s="77"/>
-      <c r="H32" s="119" t="s">
-        <v>153</v>
+      <c r="H32" s="121" t="s">
+        <v>123</v>
       </c>
       <c r="I32" s="77"/>
       <c r="J32" s="77"/>
@@ -8361,8 +8261,8 @@
       <c r="E33" s="77"/>
       <c r="F33" s="77"/>
       <c r="G33" s="77"/>
-      <c r="H33" s="108" t="s">
-        <v>124</v>
+      <c r="H33" s="109" t="s">
+        <v>66</v>
       </c>
       <c r="I33" s="77"/>
       <c r="J33" s="77"/>
@@ -8375,8 +8275,8 @@
       <c r="E34" s="77"/>
       <c r="F34" s="77"/>
       <c r="G34" s="77"/>
-      <c r="H34" s="108" t="s">
-        <v>154</v>
+      <c r="H34" s="109" t="s">
+        <v>82</v>
       </c>
       <c r="I34" s="77"/>
       <c r="J34" s="77"/>
@@ -8389,8 +8289,8 @@
       <c r="E35" s="77"/>
       <c r="F35" s="77"/>
       <c r="G35" s="77"/>
-      <c r="H35" s="119" t="s">
-        <v>139</v>
+      <c r="H35" s="121" t="s">
+        <v>119</v>
       </c>
       <c r="I35" s="77"/>
       <c r="J35" s="77"/>
@@ -8412,34 +8312,34 @@
     </row>
     <row r="36" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="89" t="s">
-        <v>155</v>
+        <v>129</v>
       </c>
       <c r="B36" s="95" t="s">
-        <v>156</v>
+        <v>130</v>
       </c>
       <c r="C36" s="95" t="s">
-        <v>157</v>
+        <v>131</v>
       </c>
       <c r="D36" s="95" t="s">
-        <v>158</v>
-      </c>
-      <c r="E36" s="116" t="s">
-        <v>159</v>
+        <v>132</v>
+      </c>
+      <c r="E36" s="118" t="s">
+        <v>133</v>
       </c>
       <c r="F36" s="95" t="s">
-        <v>158</v>
+        <v>132</v>
       </c>
       <c r="G36" s="95" t="s">
-        <v>157</v>
-      </c>
-      <c r="H36" s="120" t="s">
-        <v>160</v>
-      </c>
-      <c r="I36" s="120" t="s">
-        <v>160</v>
+        <v>131</v>
+      </c>
+      <c r="H36" s="123" t="s">
+        <v>134</v>
+      </c>
+      <c r="I36" s="123" t="s">
+        <v>134</v>
       </c>
       <c r="J36" s="103" t="s">
-        <v>161</v>
+        <v>135</v>
       </c>
       <c r="AE36" s="88" t="s">
         <v>56</v>
@@ -8462,35 +8362,35 @@
     </row>
     <row r="37" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="89"/>
-      <c r="B37" s="116" t="s">
-        <v>162</v>
-      </c>
-      <c r="C37" s="116" t="s">
-        <v>154</v>
+      <c r="B37" s="118" t="s">
+        <v>109</v>
+      </c>
+      <c r="C37" s="118" t="s">
+        <v>82</v>
       </c>
       <c r="D37" s="95" t="s">
-        <v>163</v>
-      </c>
-      <c r="E37" s="116" t="s">
-        <v>164</v>
+        <v>134</v>
+      </c>
+      <c r="E37" s="118" t="s">
+        <v>72</v>
       </c>
       <c r="F37" s="95" t="s">
-        <v>165</v>
+        <v>88</v>
       </c>
       <c r="G37" s="95" t="s">
-        <v>164</v>
-      </c>
-      <c r="H37" s="96" t="s">
-        <v>158</v>
-      </c>
-      <c r="I37" s="96" t="s">
-        <v>166</v>
-      </c>
-      <c r="J37" s="96" t="s">
-        <v>164</v>
+        <v>72</v>
+      </c>
+      <c r="H37" s="107" t="s">
+        <v>132</v>
+      </c>
+      <c r="I37" s="107" t="s">
+        <v>136</v>
+      </c>
+      <c r="J37" s="107" t="s">
+        <v>72</v>
       </c>
       <c r="AE37" s="88" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AF37" s="2" t="n">
         <v>1</v>
@@ -8510,35 +8410,35 @@
     </row>
     <row r="38" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="89"/>
-      <c r="B38" s="108" t="s">
-        <v>154</v>
-      </c>
-      <c r="C38" s="116" t="s">
-        <v>167</v>
+      <c r="B38" s="109" t="s">
+        <v>82</v>
+      </c>
+      <c r="C38" s="118" t="s">
+        <v>127</v>
       </c>
       <c r="D38" s="95" t="s">
-        <v>168</v>
-      </c>
-      <c r="E38" s="116" t="s">
-        <v>165</v>
+        <v>130</v>
+      </c>
+      <c r="E38" s="118" t="s">
+        <v>88</v>
       </c>
       <c r="F38" s="95" t="s">
-        <v>169</v>
+        <v>137</v>
       </c>
       <c r="G38" s="103" t="s">
-        <v>170</v>
-      </c>
-      <c r="H38" s="96" t="s">
-        <v>166</v>
-      </c>
-      <c r="I38" s="96" t="s">
-        <v>164</v>
+        <v>138</v>
+      </c>
+      <c r="H38" s="107" t="s">
+        <v>136</v>
+      </c>
+      <c r="I38" s="107" t="s">
+        <v>72</v>
       </c>
       <c r="J38" s="95" t="s">
-        <v>166</v>
+        <v>136</v>
       </c>
       <c r="AE38" s="99" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AF38" s="2" t="n">
         <v>1</v>
@@ -8559,66 +8459,66 @@
     <row r="39" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="89"/>
       <c r="B39" s="77"/>
-      <c r="C39" s="108" t="s">
-        <v>171</v>
+      <c r="C39" s="109" t="s">
+        <v>66</v>
       </c>
       <c r="D39" s="95" t="s">
-        <v>162</v>
+        <v>109</v>
       </c>
       <c r="E39" s="95" t="s">
-        <v>157</v>
+        <v>131</v>
       </c>
       <c r="F39" s="95" t="s">
-        <v>172</v>
+        <v>139</v>
       </c>
       <c r="G39" s="95" t="s">
-        <v>158</v>
-      </c>
-      <c r="H39" s="96" t="s">
-        <v>157</v>
-      </c>
-      <c r="I39" s="96" t="s">
-        <v>157</v>
+        <v>132</v>
+      </c>
+      <c r="H39" s="107" t="s">
+        <v>131</v>
+      </c>
+      <c r="I39" s="107" t="s">
+        <v>131</v>
       </c>
       <c r="J39" s="95" t="s">
-        <v>163</v>
+        <v>134</v>
       </c>
       <c r="AF39" s="106" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="AG39" s="106" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AH39" s="106" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="89"/>
       <c r="B40" s="77"/>
-      <c r="C40" s="108" t="s">
-        <v>125</v>
+      <c r="C40" s="109" t="s">
+        <v>64</v>
       </c>
       <c r="D40" s="95" t="s">
-        <v>125</v>
+        <v>64</v>
       </c>
       <c r="E40" s="95" t="s">
-        <v>163</v>
+        <v>134</v>
       </c>
       <c r="F40" s="95" t="s">
-        <v>173</v>
+        <v>140</v>
       </c>
       <c r="G40" s="95" t="s">
-        <v>172</v>
+        <v>139</v>
       </c>
       <c r="H40" s="95" t="s">
-        <v>164</v>
-      </c>
-      <c r="I40" s="96" t="s">
-        <v>158</v>
+        <v>72</v>
+      </c>
+      <c r="I40" s="107" t="s">
+        <v>132</v>
       </c>
       <c r="J40" s="95" t="s">
-        <v>174</v>
+        <v>141</v>
       </c>
       <c r="AE40" s="81" t="s">
         <v>18</v>
@@ -8637,26 +8537,26 @@
       <c r="A41" s="89"/>
       <c r="B41" s="77"/>
       <c r="C41" s="77"/>
-      <c r="D41" s="108" t="s">
-        <v>154</v>
+      <c r="D41" s="109" t="s">
+        <v>82</v>
       </c>
       <c r="E41" s="95" t="s">
-        <v>173</v>
-      </c>
-      <c r="F41" s="108" t="s">
-        <v>175</v>
-      </c>
-      <c r="G41" s="108" t="s">
-        <v>176</v>
+        <v>140</v>
+      </c>
+      <c r="F41" s="109" t="s">
+        <v>142</v>
+      </c>
+      <c r="G41" s="109" t="s">
+        <v>143</v>
       </c>
       <c r="H41" s="95" t="s">
-        <v>177</v>
+        <v>144</v>
       </c>
       <c r="I41" s="95" t="s">
-        <v>178</v>
+        <v>145</v>
       </c>
       <c r="J41" s="95" t="s">
-        <v>177</v>
+        <v>144</v>
       </c>
       <c r="AE41" s="32" t="s">
         <v>20</v>
@@ -8676,23 +8576,23 @@
       <c r="B42" s="77"/>
       <c r="C42" s="77"/>
       <c r="D42" s="77"/>
-      <c r="E42" s="116" t="s">
-        <v>179</v>
-      </c>
-      <c r="F42" s="108" t="s">
-        <v>154</v>
-      </c>
-      <c r="G42" s="108" t="s">
-        <v>180</v>
+      <c r="E42" s="118" t="s">
+        <v>67</v>
+      </c>
+      <c r="F42" s="109" t="s">
+        <v>82</v>
+      </c>
+      <c r="G42" s="114" t="s">
+        <v>134</v>
       </c>
       <c r="H42" s="103" t="s">
-        <v>181</v>
+        <v>146</v>
       </c>
       <c r="I42" s="103" t="s">
-        <v>170</v>
+        <v>138</v>
       </c>
       <c r="J42" s="103" t="s">
-        <v>170</v>
+        <v>138</v>
       </c>
       <c r="AE42" s="83" t="s">
         <v>22</v>
@@ -8712,23 +8612,23 @@
       <c r="B43" s="77"/>
       <c r="C43" s="77"/>
       <c r="D43" s="77"/>
-      <c r="E43" s="116" t="s">
-        <v>154</v>
-      </c>
-      <c r="F43" s="108" t="s">
-        <v>182</v>
-      </c>
-      <c r="G43" s="108" t="s">
-        <v>183</v>
+      <c r="E43" s="118" t="s">
+        <v>82</v>
+      </c>
+      <c r="F43" s="109" t="s">
+        <v>147</v>
+      </c>
+      <c r="G43" s="109" t="s">
+        <v>127</v>
       </c>
       <c r="H43" s="95" t="s">
-        <v>146</v>
+        <v>124</v>
       </c>
       <c r="I43" s="95" t="s">
-        <v>177</v>
-      </c>
-      <c r="J43" s="119" t="s">
-        <v>184</v>
+        <v>144</v>
+      </c>
+      <c r="J43" s="121" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8737,20 +8637,18 @@
       <c r="C44" s="77"/>
       <c r="D44" s="77"/>
       <c r="E44" s="95" t="s">
-        <v>158</v>
+        <v>132</v>
       </c>
       <c r="F44" s="77"/>
       <c r="G44" s="95" t="s">
-        <v>175</v>
-      </c>
-      <c r="H44" s="95" t="s">
-        <v>185</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="H44" s="95"/>
       <c r="I44" s="95" t="s">
-        <v>186</v>
+        <v>104</v>
       </c>
       <c r="J44" s="95" t="s">
-        <v>156</v>
+        <v>130</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8758,19 +8656,19 @@
       <c r="B45" s="77"/>
       <c r="C45" s="77"/>
       <c r="D45" s="77"/>
-      <c r="E45" s="116" t="s">
-        <v>186</v>
+      <c r="E45" s="118" t="s">
+        <v>104</v>
       </c>
       <c r="F45" s="77"/>
       <c r="G45" s="77"/>
-      <c r="H45" s="119" t="s">
-        <v>187</v>
+      <c r="H45" s="121" t="s">
+        <v>149</v>
       </c>
       <c r="I45" s="95" t="s">
-        <v>156</v>
+        <v>130</v>
       </c>
       <c r="J45" s="95" t="s">
-        <v>125</v>
+        <v>64</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8781,14 +8679,14 @@
       <c r="E46" s="77"/>
       <c r="F46" s="77"/>
       <c r="G46" s="77"/>
-      <c r="H46" s="108" t="s">
-        <v>171</v>
+      <c r="H46" s="109" t="s">
+        <v>66</v>
       </c>
       <c r="I46" s="95" t="s">
-        <v>171</v>
-      </c>
-      <c r="J46" s="108" t="s">
-        <v>188</v>
+        <v>66</v>
+      </c>
+      <c r="J46" s="109" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8801,7 +8699,7 @@
       <c r="G47" s="77"/>
       <c r="H47" s="77"/>
       <c r="I47" s="95" t="s">
-        <v>174</v>
+        <v>141</v>
       </c>
       <c r="J47" s="77"/>
     </row>
@@ -8815,7 +8713,7 @@
       <c r="G48" s="77"/>
       <c r="H48" s="77"/>
       <c r="I48" s="95" t="s">
-        <v>146</v>
+        <v>124</v>
       </c>
       <c r="J48" s="77"/>
     </row>
@@ -8829,7 +8727,7 @@
       <c r="G49" s="77"/>
       <c r="H49" s="77"/>
       <c r="I49" s="95" t="s">
-        <v>189</v>
+        <v>150</v>
       </c>
       <c r="J49" s="77"/>
     </row>
@@ -8843,7 +8741,7 @@
       <c r="G50" s="77"/>
       <c r="H50" s="77"/>
       <c r="I50" s="95" t="s">
-        <v>125</v>
+        <v>64</v>
       </c>
       <c r="J50" s="77"/>
     </row>
@@ -8856,8 +8754,8 @@
       <c r="F51" s="77"/>
       <c r="G51" s="77"/>
       <c r="H51" s="77"/>
-      <c r="I51" s="119" t="s">
-        <v>190</v>
+      <c r="I51" s="121" t="s">
+        <v>151</v>
       </c>
       <c r="J51" s="77"/>
     </row>
@@ -8902,245 +8800,245 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="121" t="s">
-        <v>191</v>
-      </c>
-      <c r="B1" s="121" t="s">
-        <v>192</v>
-      </c>
-      <c r="C1" s="121" t="s">
-        <v>193</v>
-      </c>
-      <c r="D1" s="121" t="s">
-        <v>194</v>
-      </c>
-      <c r="E1" s="121" t="s">
-        <v>195</v>
-      </c>
-      <c r="F1" s="121" t="s">
-        <v>196</v>
-      </c>
-      <c r="G1" s="121" t="s">
-        <v>197</v>
-      </c>
-      <c r="H1" s="122" t="s">
-        <v>198</v>
-      </c>
-      <c r="O1" s="123"/>
-      <c r="P1" s="123"/>
-      <c r="Q1" s="123"/>
-      <c r="R1" s="124"/>
-      <c r="S1" s="123"/>
-      <c r="T1" s="123"/>
-      <c r="U1" s="124"/>
-      <c r="V1" s="124"/>
+      <c r="A1" s="124" t="s">
+        <v>152</v>
+      </c>
+      <c r="B1" s="124" t="s">
+        <v>153</v>
+      </c>
+      <c r="C1" s="124" t="s">
+        <v>154</v>
+      </c>
+      <c r="D1" s="124" t="s">
+        <v>155</v>
+      </c>
+      <c r="E1" s="124" t="s">
+        <v>156</v>
+      </c>
+      <c r="F1" s="124" t="s">
+        <v>157</v>
+      </c>
+      <c r="G1" s="124" t="s">
+        <v>158</v>
+      </c>
+      <c r="H1" s="125" t="s">
+        <v>159</v>
+      </c>
+      <c r="O1" s="126"/>
+      <c r="P1" s="126"/>
+      <c r="Q1" s="126"/>
+      <c r="R1" s="127"/>
+      <c r="S1" s="126"/>
+      <c r="T1" s="126"/>
+      <c r="U1" s="127"/>
+      <c r="V1" s="127"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="125" t="n">
+      <c r="A2" s="128" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="125" t="n">
+      <c r="B2" s="128" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="125" t="s">
+      <c r="C2" s="128" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="125" t="n">
+      <c r="D2" s="128" t="n">
         <v>15.53</v>
       </c>
-      <c r="E2" s="125" t="n">
+      <c r="E2" s="128" t="n">
         <v>14.8</v>
       </c>
-      <c r="F2" s="125" t="n">
+      <c r="F2" s="128" t="n">
         <v>0.729999999999999</v>
       </c>
-      <c r="G2" s="125" t="n">
+      <c r="G2" s="128" t="n">
         <v>1.022</v>
       </c>
-      <c r="H2" s="126" t="s">
-        <v>199</v>
-      </c>
-      <c r="O2" s="123"/>
-      <c r="P2" s="123"/>
-      <c r="Q2" s="123"/>
-      <c r="R2" s="124"/>
-      <c r="S2" s="123"/>
-      <c r="T2" s="123"/>
-      <c r="U2" s="127"/>
-      <c r="V2" s="123"/>
+      <c r="H2" s="129" t="s">
+        <v>160</v>
+      </c>
+      <c r="O2" s="126"/>
+      <c r="P2" s="126"/>
+      <c r="Q2" s="126"/>
+      <c r="R2" s="127"/>
+      <c r="S2" s="126"/>
+      <c r="T2" s="126"/>
+      <c r="U2" s="130"/>
+      <c r="V2" s="126"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="125" t="n">
+      <c r="A3" s="128" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="125" t="n">
+      <c r="B3" s="128" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="125" t="s">
+      <c r="C3" s="128" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="125" t="n">
+      <c r="D3" s="128" t="n">
         <v>14.8</v>
       </c>
-      <c r="E3" s="125" t="n">
+      <c r="E3" s="128" t="n">
         <v>14.02</v>
       </c>
-      <c r="F3" s="125" t="n">
+      <c r="F3" s="128" t="n">
         <v>0.780000000000001</v>
       </c>
-      <c r="G3" s="125" t="n">
+      <c r="G3" s="128" t="n">
         <v>1.092</v>
       </c>
-      <c r="H3" s="126" t="s">
-        <v>200</v>
-      </c>
-      <c r="O3" s="123"/>
-      <c r="P3" s="123"/>
-      <c r="Q3" s="128"/>
-      <c r="R3" s="124"/>
-      <c r="S3" s="123"/>
-      <c r="T3" s="123"/>
-      <c r="U3" s="127"/>
-      <c r="V3" s="123"/>
+      <c r="H3" s="129" t="s">
+        <v>161</v>
+      </c>
+      <c r="O3" s="126"/>
+      <c r="P3" s="126"/>
+      <c r="Q3" s="131"/>
+      <c r="R3" s="127"/>
+      <c r="S3" s="126"/>
+      <c r="T3" s="126"/>
+      <c r="U3" s="130"/>
+      <c r="V3" s="126"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="125" t="n">
+      <c r="A4" s="128" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="125" t="n">
+      <c r="B4" s="128" t="n">
         <v>3</v>
       </c>
-      <c r="C4" s="125" t="s">
+      <c r="C4" s="128" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="125" t="n">
+      <c r="D4" s="128" t="n">
         <v>12.4</v>
       </c>
-      <c r="E4" s="125" t="n">
+      <c r="E4" s="128" t="n">
         <v>11.48</v>
       </c>
-      <c r="F4" s="125" t="n">
+      <c r="F4" s="128" t="n">
         <v>0.92</v>
       </c>
-      <c r="G4" s="125" t="n">
+      <c r="G4" s="128" t="n">
         <v>1.288</v>
       </c>
-      <c r="H4" s="126" t="s">
-        <v>201</v>
-      </c>
-      <c r="O4" s="129"/>
-      <c r="P4" s="129"/>
-      <c r="Q4" s="129"/>
-      <c r="R4" s="130"/>
-      <c r="S4" s="129"/>
-      <c r="T4" s="129"/>
-      <c r="U4" s="131"/>
-      <c r="V4" s="123"/>
+      <c r="H4" s="129" t="s">
+        <v>162</v>
+      </c>
+      <c r="O4" s="132"/>
+      <c r="P4" s="132"/>
+      <c r="Q4" s="132"/>
+      <c r="R4" s="133"/>
+      <c r="S4" s="132"/>
+      <c r="T4" s="132"/>
+      <c r="U4" s="134"/>
+      <c r="V4" s="126"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="125" t="n">
+      <c r="A5" s="128" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="125" t="n">
+      <c r="B5" s="128" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="125" t="s">
+      <c r="C5" s="128" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="125" t="n">
+      <c r="D5" s="128" t="n">
         <v>13.31</v>
       </c>
-      <c r="E5" s="125" t="n">
+      <c r="E5" s="128" t="n">
         <v>12.89</v>
       </c>
-      <c r="F5" s="125" t="n">
+      <c r="F5" s="128" t="n">
         <v>0.42</v>
       </c>
-      <c r="G5" s="125" t="n">
+      <c r="G5" s="128" t="n">
         <v>0.588</v>
       </c>
-      <c r="H5" s="126" t="s">
-        <v>202</v>
+      <c r="H5" s="129" t="s">
+        <v>163</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="K5" s="132" t="n">
+        <v>164</v>
+      </c>
+      <c r="K5" s="135" t="n">
         <v>204.498</v>
       </c>
-      <c r="O5" s="130"/>
-      <c r="P5" s="130"/>
-      <c r="Q5" s="129"/>
-      <c r="R5" s="130"/>
-      <c r="S5" s="130"/>
-      <c r="T5" s="130"/>
-      <c r="U5" s="131"/>
-      <c r="V5" s="124"/>
+      <c r="O5" s="133"/>
+      <c r="P5" s="133"/>
+      <c r="Q5" s="132"/>
+      <c r="R5" s="133"/>
+      <c r="S5" s="133"/>
+      <c r="T5" s="133"/>
+      <c r="U5" s="134"/>
+      <c r="V5" s="127"/>
     </row>
     <row r="6" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="125" t="n">
+      <c r="A6" s="128" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="125" t="n">
+      <c r="B6" s="128" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="125" t="s">
+      <c r="C6" s="128" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="125" t="n">
+      <c r="D6" s="128" t="n">
         <v>11.12</v>
       </c>
-      <c r="E6" s="125" t="n">
+      <c r="E6" s="128" t="n">
         <v>-0.06</v>
       </c>
-      <c r="F6" s="125" t="n">
+      <c r="F6" s="128" t="n">
         <v>11.18</v>
       </c>
-      <c r="G6" s="125" t="n">
+      <c r="G6" s="128" t="n">
         <v>15.652</v>
       </c>
-      <c r="H6" s="126" t="s">
-        <v>204</v>
-      </c>
-      <c r="I6" s="133" t="s">
-        <v>205</v>
-      </c>
-      <c r="J6" s="134" t="s">
-        <v>206</v>
-      </c>
-      <c r="O6" s="123"/>
-      <c r="P6" s="123"/>
-      <c r="Q6" s="123"/>
-      <c r="R6" s="124"/>
-      <c r="S6" s="123"/>
-      <c r="T6" s="123"/>
-      <c r="U6" s="131"/>
-      <c r="V6" s="123"/>
+      <c r="H6" s="129" t="s">
+        <v>165</v>
+      </c>
+      <c r="I6" s="136" t="s">
+        <v>166</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="O6" s="126"/>
+      <c r="P6" s="126"/>
+      <c r="Q6" s="126"/>
+      <c r="R6" s="127"/>
+      <c r="S6" s="126"/>
+      <c r="T6" s="126"/>
+      <c r="U6" s="134"/>
+      <c r="V6" s="126"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="125" t="n">
+      <c r="A7" s="128" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="125" t="n">
+      <c r="B7" s="128" t="n">
         <v>3</v>
       </c>
-      <c r="C7" s="125" t="s">
+      <c r="C7" s="128" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="125" t="n">
+      <c r="D7" s="128" t="n">
         <v>9.73</v>
       </c>
-      <c r="E7" s="125" t="n">
+      <c r="E7" s="128" t="n">
         <v>9.25</v>
       </c>
-      <c r="F7" s="125" t="n">
+      <c r="F7" s="128" t="n">
         <v>0.48</v>
       </c>
-      <c r="G7" s="125" t="n">
+      <c r="G7" s="128" t="n">
         <v>0.672000000000001</v>
       </c>
-      <c r="H7" s="126" t="s">
-        <v>207</v>
+      <c r="H7" s="129" t="s">
+        <v>168</v>
       </c>
       <c r="J7" s="1" t="s">
         <v>20</v>
@@ -9149,80 +9047,80 @@
         <f aca="false">AVERAGE(G2:G10)</f>
         <v>2.54333333333333</v>
       </c>
-      <c r="O7" s="129"/>
-      <c r="P7" s="129"/>
-      <c r="Q7" s="129"/>
-      <c r="R7" s="130"/>
-      <c r="S7" s="129"/>
-      <c r="T7" s="129"/>
-      <c r="U7" s="135"/>
-      <c r="V7" s="123"/>
+      <c r="O7" s="132"/>
+      <c r="P7" s="132"/>
+      <c r="Q7" s="132"/>
+      <c r="R7" s="133"/>
+      <c r="S7" s="132"/>
+      <c r="T7" s="132"/>
+      <c r="U7" s="137"/>
+      <c r="V7" s="126"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="125" t="n">
+      <c r="A8" s="128" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="125" t="n">
+      <c r="B8" s="128" t="n">
         <v>1</v>
       </c>
-      <c r="C8" s="125" t="s">
+      <c r="C8" s="128" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="125" t="n">
+      <c r="D8" s="128" t="n">
         <v>14.02</v>
       </c>
-      <c r="E8" s="125" t="n">
+      <c r="E8" s="128" t="n">
         <v>13.31</v>
       </c>
-      <c r="F8" s="125" t="n">
+      <c r="F8" s="128" t="n">
         <v>0.709999999999999</v>
       </c>
-      <c r="G8" s="125" t="n">
+      <c r="G8" s="128" t="n">
         <v>0.993999999999999</v>
       </c>
-      <c r="H8" s="126" t="s">
-        <v>208</v>
+      <c r="H8" s="129" t="s">
+        <v>169</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>209</v>
+        <v>170</v>
       </c>
       <c r="K8" s="1" t="n">
         <f aca="false">AVERAGE(G11:G19)</f>
         <v>14.896</v>
       </c>
-      <c r="O8" s="123"/>
-      <c r="P8" s="123"/>
-      <c r="Q8" s="123"/>
-      <c r="R8" s="124"/>
-      <c r="S8" s="123"/>
-      <c r="T8" s="123"/>
-      <c r="U8" s="136"/>
-      <c r="V8" s="123"/>
+      <c r="O8" s="126"/>
+      <c r="P8" s="126"/>
+      <c r="Q8" s="126"/>
+      <c r="R8" s="127"/>
+      <c r="S8" s="126"/>
+      <c r="T8" s="126"/>
+      <c r="U8" s="138"/>
+      <c r="V8" s="126"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="125" t="n">
+      <c r="A9" s="128" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="125" t="n">
+      <c r="B9" s="128" t="n">
         <v>2</v>
       </c>
-      <c r="C9" s="125" t="s">
+      <c r="C9" s="128" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="125" t="n">
+      <c r="D9" s="128" t="n">
         <v>9.25</v>
       </c>
-      <c r="E9" s="125" t="n">
+      <c r="E9" s="128" t="n">
         <v>8.57</v>
       </c>
-      <c r="F9" s="125" t="n">
+      <c r="F9" s="128" t="n">
         <v>0.68</v>
       </c>
-      <c r="G9" s="125" t="n">
+      <c r="G9" s="128" t="n">
         <v>0.952</v>
       </c>
-      <c r="H9" s="126" t="s">
-        <v>210</v>
+      <c r="H9" s="129" t="s">
+        <v>171</v>
       </c>
       <c r="J9" s="1" t="s">
         <v>22</v>
@@ -9231,563 +9129,563 @@
         <f aca="false">AVERAGE(G20:G28)</f>
         <v>5.28266666666667</v>
       </c>
-      <c r="O9" s="123"/>
-      <c r="P9" s="123"/>
-      <c r="Q9" s="123"/>
-      <c r="R9" s="124"/>
-      <c r="S9" s="123"/>
-      <c r="T9" s="123"/>
-      <c r="U9" s="137"/>
-      <c r="V9" s="124"/>
+      <c r="O9" s="126"/>
+      <c r="P9" s="126"/>
+      <c r="Q9" s="126"/>
+      <c r="R9" s="127"/>
+      <c r="S9" s="126"/>
+      <c r="T9" s="126"/>
+      <c r="U9" s="139"/>
+      <c r="V9" s="127"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="125" t="n">
+      <c r="A10" s="128" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="125" t="n">
+      <c r="B10" s="128" t="n">
         <v>3</v>
       </c>
-      <c r="C10" s="125" t="s">
+      <c r="C10" s="128" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="125" t="n">
+      <c r="D10" s="128" t="n">
         <v>8.57</v>
       </c>
-      <c r="E10" s="125" t="n">
+      <c r="E10" s="128" t="n">
         <v>8.12</v>
       </c>
-      <c r="F10" s="125" t="n">
+      <c r="F10" s="128" t="n">
         <v>0.450000000000001</v>
       </c>
-      <c r="G10" s="125" t="n">
+      <c r="G10" s="128" t="n">
         <v>0.630000000000001</v>
       </c>
-      <c r="H10" s="126" t="s">
-        <v>211</v>
-      </c>
-      <c r="O10" s="123"/>
-      <c r="P10" s="123"/>
-      <c r="Q10" s="123"/>
-      <c r="R10" s="124"/>
-      <c r="S10" s="123"/>
-      <c r="T10" s="123"/>
-      <c r="U10" s="137"/>
-      <c r="V10" s="124"/>
+      <c r="H10" s="129" t="s">
+        <v>172</v>
+      </c>
+      <c r="O10" s="126"/>
+      <c r="P10" s="126"/>
+      <c r="Q10" s="126"/>
+      <c r="R10" s="127"/>
+      <c r="S10" s="126"/>
+      <c r="T10" s="126"/>
+      <c r="U10" s="139"/>
+      <c r="V10" s="127"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="125" t="n">
+      <c r="A11" s="128" t="n">
         <v>1</v>
       </c>
-      <c r="B11" s="125" t="n">
+      <c r="B11" s="128" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="125" t="s">
+      <c r="C11" s="128" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="125" t="n">
+      <c r="D11" s="128" t="n">
         <v>14.44</v>
       </c>
-      <c r="E11" s="125" t="n">
+      <c r="E11" s="128" t="n">
         <v>4.33</v>
       </c>
-      <c r="F11" s="125" t="n">
+      <c r="F11" s="128" t="n">
         <v>10.11</v>
       </c>
-      <c r="G11" s="125" t="n">
+      <c r="G11" s="128" t="n">
         <v>14.154</v>
       </c>
-      <c r="H11" s="126" t="s">
-        <v>212</v>
-      </c>
-      <c r="O11" s="124"/>
-      <c r="P11" s="124"/>
-      <c r="Q11" s="124"/>
-      <c r="R11" s="124"/>
-      <c r="S11" s="124"/>
-      <c r="T11" s="124"/>
-      <c r="U11" s="137"/>
-      <c r="V11" s="124"/>
+      <c r="H11" s="129" t="s">
+        <v>173</v>
+      </c>
+      <c r="O11" s="127"/>
+      <c r="P11" s="127"/>
+      <c r="Q11" s="127"/>
+      <c r="R11" s="127"/>
+      <c r="S11" s="127"/>
+      <c r="T11" s="127"/>
+      <c r="U11" s="139"/>
+      <c r="V11" s="127"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="125" t="n">
+      <c r="A12" s="128" t="n">
         <v>1</v>
       </c>
-      <c r="B12" s="125" t="n">
+      <c r="B12" s="128" t="n">
         <v>2</v>
       </c>
-      <c r="C12" s="125" t="s">
-        <v>213</v>
-      </c>
-      <c r="D12" s="125" t="n">
+      <c r="C12" s="128" t="s">
+        <v>174</v>
+      </c>
+      <c r="D12" s="128" t="n">
         <v>21.02</v>
       </c>
-      <c r="E12" s="138" t="n">
+      <c r="E12" s="140" t="n">
         <v>10.83</v>
       </c>
-      <c r="F12" s="125" t="n">
+      <c r="F12" s="128" t="n">
         <v>10.19</v>
       </c>
-      <c r="G12" s="125" t="n">
+      <c r="G12" s="128" t="n">
         <v>14.266</v>
       </c>
-      <c r="H12" s="126" t="s">
-        <v>214</v>
-      </c>
-      <c r="O12" s="129"/>
-      <c r="P12" s="129"/>
-      <c r="Q12" s="129"/>
-      <c r="R12" s="130"/>
-      <c r="S12" s="129"/>
-      <c r="T12" s="129"/>
-      <c r="U12" s="137"/>
-      <c r="V12" s="123"/>
+      <c r="H12" s="129" t="s">
+        <v>175</v>
+      </c>
+      <c r="O12" s="132"/>
+      <c r="P12" s="132"/>
+      <c r="Q12" s="132"/>
+      <c r="R12" s="133"/>
+      <c r="S12" s="132"/>
+      <c r="T12" s="132"/>
+      <c r="U12" s="139"/>
+      <c r="V12" s="126"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="125" t="n">
+      <c r="A13" s="128" t="n">
         <v>1</v>
       </c>
-      <c r="B13" s="125" t="n">
+      <c r="B13" s="128" t="n">
         <v>3</v>
       </c>
-      <c r="C13" s="125" t="s">
-        <v>213</v>
-      </c>
-      <c r="D13" s="125" t="n">
+      <c r="C13" s="128" t="s">
+        <v>174</v>
+      </c>
+      <c r="D13" s="128" t="n">
         <v>15.83</v>
       </c>
-      <c r="E13" s="125" t="n">
+      <c r="E13" s="128" t="n">
         <v>6.12</v>
       </c>
-      <c r="F13" s="125" t="n">
+      <c r="F13" s="128" t="n">
         <v>9.71</v>
       </c>
-      <c r="G13" s="125" t="n">
+      <c r="G13" s="128" t="n">
         <v>13.594</v>
       </c>
-      <c r="H13" s="126" t="s">
-        <v>215</v>
-      </c>
-      <c r="O13" s="123"/>
-      <c r="P13" s="123"/>
-      <c r="Q13" s="123"/>
-      <c r="R13" s="124"/>
-      <c r="S13" s="123"/>
-      <c r="T13" s="123"/>
-      <c r="U13" s="137"/>
-      <c r="V13" s="123"/>
+      <c r="H13" s="129" t="s">
+        <v>176</v>
+      </c>
+      <c r="O13" s="126"/>
+      <c r="P13" s="126"/>
+      <c r="Q13" s="126"/>
+      <c r="R13" s="127"/>
+      <c r="S13" s="126"/>
+      <c r="T13" s="126"/>
+      <c r="U13" s="139"/>
+      <c r="V13" s="126"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="125" t="n">
+      <c r="A14" s="128" t="n">
         <v>3</v>
       </c>
-      <c r="B14" s="125" t="n">
+      <c r="B14" s="128" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="125" t="s">
+      <c r="C14" s="128" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="125" t="n">
+      <c r="D14" s="128" t="n">
         <v>14.46</v>
       </c>
-      <c r="E14" s="125" t="n">
+      <c r="E14" s="128" t="n">
         <v>3.98</v>
       </c>
-      <c r="F14" s="125" t="n">
+      <c r="F14" s="128" t="n">
         <v>10.48</v>
       </c>
-      <c r="G14" s="125" t="n">
+      <c r="G14" s="128" t="n">
         <v>14.672</v>
       </c>
-      <c r="H14" s="126" t="s">
-        <v>216</v>
-      </c>
-      <c r="O14" s="123"/>
-      <c r="P14" s="123"/>
-      <c r="Q14" s="123"/>
-      <c r="R14" s="124"/>
-      <c r="S14" s="123"/>
-      <c r="T14" s="123"/>
-      <c r="U14" s="137"/>
-      <c r="V14" s="124"/>
+      <c r="H14" s="129" t="s">
+        <v>177</v>
+      </c>
+      <c r="O14" s="126"/>
+      <c r="P14" s="126"/>
+      <c r="Q14" s="126"/>
+      <c r="R14" s="127"/>
+      <c r="S14" s="126"/>
+      <c r="T14" s="126"/>
+      <c r="U14" s="139"/>
+      <c r="V14" s="127"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="125" t="n">
+      <c r="A15" s="128" t="n">
         <v>3</v>
       </c>
-      <c r="B15" s="125" t="n">
+      <c r="B15" s="128" t="n">
         <v>2</v>
       </c>
-      <c r="C15" s="125" t="s">
+      <c r="C15" s="128" t="s">
         <v>18</v>
       </c>
-      <c r="D15" s="125" t="n">
+      <c r="D15" s="128" t="n">
         <v>26.12</v>
       </c>
-      <c r="E15" s="125" t="n">
+      <c r="E15" s="128" t="n">
         <v>11.85</v>
       </c>
-      <c r="F15" s="125" t="n">
+      <c r="F15" s="128" t="n">
         <v>14.27</v>
       </c>
-      <c r="G15" s="125" t="n">
+      <c r="G15" s="128" t="n">
         <v>19.978</v>
       </c>
-      <c r="H15" s="126" t="s">
-        <v>217</v>
-      </c>
-      <c r="O15" s="129"/>
-      <c r="P15" s="129"/>
-      <c r="Q15" s="129"/>
-      <c r="R15" s="130"/>
-      <c r="S15" s="129"/>
-      <c r="T15" s="129"/>
-      <c r="U15" s="137"/>
-      <c r="V15" s="130"/>
+      <c r="H15" s="129" t="s">
+        <v>178</v>
+      </c>
+      <c r="O15" s="132"/>
+      <c r="P15" s="132"/>
+      <c r="Q15" s="132"/>
+      <c r="R15" s="133"/>
+      <c r="S15" s="132"/>
+      <c r="T15" s="132"/>
+      <c r="U15" s="139"/>
+      <c r="V15" s="133"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="125" t="n">
+      <c r="A16" s="128" t="n">
         <v>3</v>
       </c>
-      <c r="B16" s="125" t="n">
+      <c r="B16" s="128" t="n">
         <v>3</v>
       </c>
-      <c r="C16" s="125" t="s">
+      <c r="C16" s="128" t="s">
         <v>18</v>
       </c>
-      <c r="D16" s="125" t="n">
+      <c r="D16" s="128" t="n">
         <v>31.85</v>
       </c>
-      <c r="E16" s="125" t="n">
+      <c r="E16" s="128" t="n">
         <v>19.91</v>
       </c>
-      <c r="F16" s="125" t="n">
+      <c r="F16" s="128" t="n">
         <v>11.94</v>
       </c>
-      <c r="G16" s="125" t="n">
+      <c r="G16" s="128" t="n">
         <v>16.716</v>
       </c>
-      <c r="H16" s="126" t="s">
-        <v>218</v>
-      </c>
-      <c r="O16" s="129"/>
-      <c r="P16" s="129"/>
-      <c r="Q16" s="129"/>
-      <c r="R16" s="130"/>
-      <c r="S16" s="129"/>
-      <c r="T16" s="130"/>
-      <c r="U16" s="136"/>
-      <c r="V16" s="130"/>
+      <c r="H16" s="129" t="s">
+        <v>179</v>
+      </c>
+      <c r="O16" s="132"/>
+      <c r="P16" s="132"/>
+      <c r="Q16" s="132"/>
+      <c r="R16" s="133"/>
+      <c r="S16" s="132"/>
+      <c r="T16" s="133"/>
+      <c r="U16" s="138"/>
+      <c r="V16" s="133"/>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="125" t="n">
+      <c r="A17" s="128" t="n">
         <v>6</v>
       </c>
-      <c r="B17" s="125" t="n">
+      <c r="B17" s="128" t="n">
         <v>1</v>
       </c>
-      <c r="C17" s="125" t="s">
+      <c r="C17" s="128" t="s">
         <v>18</v>
       </c>
-      <c r="D17" s="125" t="n">
+      <c r="D17" s="128" t="n">
         <v>24.33</v>
       </c>
-      <c r="E17" s="125" t="n">
+      <c r="E17" s="128" t="n">
         <v>14.46</v>
       </c>
-      <c r="F17" s="125" t="n">
+      <c r="F17" s="128" t="n">
         <v>9.87</v>
       </c>
-      <c r="G17" s="125" t="n">
+      <c r="G17" s="128" t="n">
         <v>13.818</v>
       </c>
-      <c r="H17" s="126" t="s">
-        <v>219</v>
+      <c r="H17" s="129" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="125" t="n">
+      <c r="A18" s="128" t="n">
         <v>6</v>
       </c>
-      <c r="B18" s="125" t="n">
+      <c r="B18" s="128" t="n">
         <v>2</v>
       </c>
-      <c r="C18" s="125" t="s">
+      <c r="C18" s="128" t="s">
         <v>18</v>
       </c>
-      <c r="D18" s="125" t="n">
+      <c r="D18" s="128" t="n">
         <v>19.79</v>
       </c>
-      <c r="E18" s="125" t="n">
+      <c r="E18" s="128" t="n">
         <v>9.3</v>
       </c>
-      <c r="F18" s="125" t="n">
+      <c r="F18" s="128" t="n">
         <v>10.49</v>
       </c>
-      <c r="G18" s="125" t="n">
+      <c r="G18" s="128" t="n">
         <v>14.686</v>
       </c>
-      <c r="H18" s="126" t="s">
-        <v>220</v>
+      <c r="H18" s="129" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="125" t="n">
+      <c r="A19" s="128" t="n">
         <v>6</v>
       </c>
-      <c r="B19" s="125" t="n">
+      <c r="B19" s="128" t="n">
         <v>3</v>
       </c>
-      <c r="C19" s="125" t="s">
+      <c r="C19" s="128" t="s">
         <v>18</v>
       </c>
-      <c r="D19" s="125" t="n">
+      <c r="D19" s="128" t="n">
         <v>14.3</v>
       </c>
-      <c r="E19" s="125" t="n">
+      <c r="E19" s="128" t="n">
         <v>5.6</v>
       </c>
-      <c r="F19" s="125" t="n">
+      <c r="F19" s="128" t="n">
         <v>8.7</v>
       </c>
-      <c r="G19" s="125" t="n">
+      <c r="G19" s="128" t="n">
         <v>12.18</v>
       </c>
-      <c r="H19" s="126" t="s">
-        <v>221</v>
+      <c r="H19" s="129" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="125" t="n">
+      <c r="A20" s="128" t="n">
         <v>1</v>
       </c>
-      <c r="B20" s="125" t="n">
+      <c r="B20" s="128" t="n">
         <v>1</v>
       </c>
-      <c r="C20" s="125" t="s">
+      <c r="C20" s="128" t="s">
         <v>22</v>
       </c>
-      <c r="D20" s="125" t="n">
+      <c r="D20" s="128" t="n">
         <v>10</v>
       </c>
-      <c r="E20" s="125" t="n">
+      <c r="E20" s="128" t="n">
         <v>6.53</v>
       </c>
-      <c r="F20" s="125" t="n">
+      <c r="F20" s="128" t="n">
         <v>3.47</v>
       </c>
-      <c r="G20" s="125" t="n">
+      <c r="G20" s="128" t="n">
         <v>4.858</v>
       </c>
-      <c r="H20" s="126" t="s">
-        <v>222</v>
+      <c r="H20" s="129" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="125" t="n">
+      <c r="A21" s="128" t="n">
         <v>1</v>
       </c>
-      <c r="B21" s="125" t="n">
+      <c r="B21" s="128" t="n">
         <v>2</v>
       </c>
-      <c r="C21" s="125" t="s">
+      <c r="C21" s="128" t="s">
         <v>22</v>
       </c>
-      <c r="D21" s="125" t="n">
+      <c r="D21" s="128" t="n">
         <v>11.62</v>
       </c>
-      <c r="E21" s="125" t="n">
+      <c r="E21" s="128" t="n">
         <v>8.1</v>
       </c>
-      <c r="F21" s="125" t="n">
+      <c r="F21" s="128" t="n">
         <v>3.52</v>
       </c>
-      <c r="G21" s="125" t="n">
+      <c r="G21" s="128" t="n">
         <v>4.928</v>
       </c>
-      <c r="H21" s="126" t="s">
-        <v>223</v>
+      <c r="H21" s="129" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="125" t="n">
+      <c r="A22" s="128" t="n">
         <v>1</v>
       </c>
-      <c r="B22" s="125" t="n">
+      <c r="B22" s="128" t="n">
         <v>3</v>
       </c>
-      <c r="C22" s="125" t="s">
+      <c r="C22" s="128" t="s">
         <v>22</v>
       </c>
-      <c r="D22" s="125" t="n">
+      <c r="D22" s="128" t="n">
         <v>8.1</v>
       </c>
-      <c r="E22" s="125" t="n">
+      <c r="E22" s="128" t="n">
         <v>5.01</v>
       </c>
-      <c r="F22" s="125" t="n">
+      <c r="F22" s="128" t="n">
         <v>3.09</v>
       </c>
-      <c r="G22" s="125" t="n">
+      <c r="G22" s="128" t="n">
         <v>4.326</v>
       </c>
-      <c r="H22" s="126" t="s">
-        <v>224</v>
+      <c r="H22" s="129" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="139" t="n">
+      <c r="A23" s="141" t="n">
         <v>3</v>
       </c>
-      <c r="B23" s="139" t="n">
+      <c r="B23" s="141" t="n">
         <v>1</v>
       </c>
-      <c r="C23" s="139" t="s">
+      <c r="C23" s="141" t="s">
         <v>22</v>
       </c>
-      <c r="D23" s="139" t="n">
+      <c r="D23" s="141" t="n">
         <v>6.53</v>
       </c>
-      <c r="E23" s="139" t="n">
+      <c r="E23" s="141" t="n">
         <v>3.1</v>
       </c>
-      <c r="F23" s="139" t="n">
+      <c r="F23" s="141" t="n">
         <v>3.43</v>
       </c>
-      <c r="G23" s="139" t="n">
+      <c r="G23" s="141" t="n">
         <v>4.802</v>
       </c>
-      <c r="H23" s="140" t="s">
-        <v>225</v>
+      <c r="H23" s="142" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="125" t="n">
+      <c r="A24" s="128" t="n">
         <v>3</v>
       </c>
-      <c r="B24" s="125" t="n">
+      <c r="B24" s="128" t="n">
         <v>2</v>
       </c>
-      <c r="C24" s="125" t="s">
+      <c r="C24" s="128" t="s">
         <v>22</v>
       </c>
-      <c r="D24" s="125" t="n">
+      <c r="D24" s="128" t="n">
         <v>21</v>
       </c>
-      <c r="E24" s="125" t="n">
+      <c r="E24" s="128" t="n">
         <v>16.58</v>
       </c>
-      <c r="F24" s="125" t="n">
+      <c r="F24" s="128" t="n">
         <v>4.42</v>
       </c>
-      <c r="G24" s="125" t="n">
+      <c r="G24" s="128" t="n">
         <v>6.188</v>
       </c>
-      <c r="H24" s="126" t="s">
-        <v>226</v>
+      <c r="H24" s="129" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="125" t="n">
+      <c r="A25" s="128" t="n">
         <v>3</v>
       </c>
-      <c r="B25" s="125" t="n">
+      <c r="B25" s="128" t="n">
         <v>3</v>
       </c>
-      <c r="C25" s="125" t="s">
+      <c r="C25" s="128" t="s">
         <v>22</v>
       </c>
-      <c r="D25" s="125" t="n">
+      <c r="D25" s="128" t="n">
         <v>16.58</v>
       </c>
-      <c r="E25" s="125" t="n">
+      <c r="E25" s="128" t="n">
         <v>13.21</v>
       </c>
-      <c r="F25" s="125" t="n">
+      <c r="F25" s="128" t="n">
         <v>3.37</v>
       </c>
-      <c r="G25" s="125" t="n">
+      <c r="G25" s="128" t="n">
         <v>4.718</v>
       </c>
-      <c r="H25" s="126" t="s">
-        <v>227</v>
+      <c r="H25" s="129" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="125" t="n">
+      <c r="A26" s="128" t="n">
         <v>6</v>
       </c>
-      <c r="B26" s="125" t="n">
+      <c r="B26" s="128" t="n">
         <v>1</v>
       </c>
-      <c r="C26" s="125" t="s">
+      <c r="C26" s="128" t="s">
         <v>22</v>
       </c>
-      <c r="D26" s="125" t="n">
+      <c r="D26" s="128" t="n">
         <v>8.14</v>
       </c>
-      <c r="E26" s="125" t="n">
+      <c r="E26" s="128" t="n">
         <v>1.2</v>
       </c>
-      <c r="F26" s="125" t="n">
+      <c r="F26" s="128" t="n">
         <v>6.94</v>
       </c>
-      <c r="G26" s="125" t="n">
+      <c r="G26" s="128" t="n">
         <v>9.716</v>
       </c>
-      <c r="H26" s="126" t="s">
-        <v>228</v>
+      <c r="H26" s="129" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="125" t="n">
+      <c r="A27" s="128" t="n">
         <v>6</v>
       </c>
-      <c r="B27" s="125" t="n">
+      <c r="B27" s="128" t="n">
         <v>2</v>
       </c>
-      <c r="C27" s="125" t="s">
+      <c r="C27" s="128" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="125" t="n">
+      <c r="D27" s="128" t="n">
         <v>13.21</v>
       </c>
-      <c r="E27" s="125" t="n">
+      <c r="E27" s="128" t="n">
         <v>10.21</v>
       </c>
-      <c r="F27" s="125" t="n">
+      <c r="F27" s="128" t="n">
         <v>3</v>
       </c>
-      <c r="G27" s="125" t="n">
+      <c r="G27" s="128" t="n">
         <v>4.2</v>
       </c>
-      <c r="H27" s="126" t="s">
-        <v>229</v>
+      <c r="H27" s="129" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="125" t="n">
+      <c r="A28" s="128" t="n">
         <v>6</v>
       </c>
-      <c r="B28" s="125" t="n">
+      <c r="B28" s="128" t="n">
         <v>3</v>
       </c>
-      <c r="C28" s="125" t="s">
+      <c r="C28" s="128" t="s">
         <v>22</v>
       </c>
-      <c r="D28" s="125" t="n">
+      <c r="D28" s="128" t="n">
         <v>10.21</v>
       </c>
-      <c r="E28" s="125" t="n">
+      <c r="E28" s="128" t="n">
         <v>7.49</v>
       </c>
-      <c r="F28" s="125" t="n">
+      <c r="F28" s="128" t="n">
         <v>2.72</v>
       </c>
-      <c r="G28" s="125" t="n">
+      <c r="G28" s="128" t="n">
         <v>3.808</v>
       </c>
-      <c r="H28" s="126" t="s">
-        <v>230</v>
+      <c r="H28" s="129" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9827,760 +9725,760 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="141" t="s">
+      <c r="A1" s="143" t="s">
+        <v>192</v>
+      </c>
+      <c r="B1" s="143" t="s">
+        <v>193</v>
+      </c>
+      <c r="C1" s="143" t="s">
+        <v>194</v>
+      </c>
+      <c r="D1" s="144" t="s">
+        <v>195</v>
+      </c>
+      <c r="E1" s="143" t="s">
+        <v>196</v>
+      </c>
+      <c r="F1" s="143" t="s">
+        <v>197</v>
+      </c>
+      <c r="G1" s="144" t="s">
+        <v>198</v>
+      </c>
+      <c r="H1" s="144" t="s">
+        <v>199</v>
+      </c>
+      <c r="I1" s="145" t="s">
+        <v>200</v>
+      </c>
+      <c r="J1" s="145" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="143" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="143" t="s">
+        <v>202</v>
+      </c>
+      <c r="C2" s="143" t="s">
+        <v>203</v>
+      </c>
+      <c r="D2" s="144" t="s">
+        <v>204</v>
+      </c>
+      <c r="E2" s="143" t="n">
+        <v>8</v>
+      </c>
+      <c r="F2" s="143" t="n">
+        <v>8</v>
+      </c>
+      <c r="G2" s="146" t="s">
+        <v>205</v>
+      </c>
+      <c r="H2" s="143" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="I2" s="145" t="n">
+        <v>3.3135</v>
+      </c>
+      <c r="J2" s="145" t="n">
+        <v>3.3135</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="143" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="143" t="s">
+        <v>202</v>
+      </c>
+      <c r="C3" s="147" t="s">
+        <v>206</v>
+      </c>
+      <c r="D3" s="144" t="s">
+        <v>207</v>
+      </c>
+      <c r="E3" s="143" t="n">
+        <v>8</v>
+      </c>
+      <c r="F3" s="143" t="n">
+        <v>8</v>
+      </c>
+      <c r="G3" s="146" t="s">
+        <v>208</v>
+      </c>
+      <c r="H3" s="143" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="I3" s="145" t="n">
+        <v>3.3135</v>
+      </c>
+      <c r="J3" s="145" t="n">
+        <v>3.3135</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="148" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="148" t="s">
+        <v>209</v>
+      </c>
+      <c r="C4" s="148" t="s">
+        <v>210</v>
+      </c>
+      <c r="D4" s="149" t="s">
+        <v>204</v>
+      </c>
+      <c r="E4" s="148" t="n">
+        <v>8</v>
+      </c>
+      <c r="F4" s="148" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="150" t="s">
+        <v>211</v>
+      </c>
+      <c r="H4" s="143" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="I4" s="145" t="n">
+        <v>2.9046</v>
+      </c>
+      <c r="J4" s="145" t="n">
+        <v>2.9046</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="149" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="149" t="s">
+        <v>209</v>
+      </c>
+      <c r="C5" s="148" t="s">
+        <v>212</v>
+      </c>
+      <c r="D5" s="149" t="s">
+        <v>213</v>
+      </c>
+      <c r="E5" s="149" t="n">
+        <v>8</v>
+      </c>
+      <c r="F5" s="149" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="150" t="s">
+        <v>214</v>
+      </c>
+      <c r="H5" s="144" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="145" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="145" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="143" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="143" t="s">
+        <v>215</v>
+      </c>
+      <c r="C6" s="143" t="s">
+        <v>216</v>
+      </c>
+      <c r="D6" s="144" t="s">
+        <v>217</v>
+      </c>
+      <c r="E6" s="143" t="n">
+        <v>8</v>
+      </c>
+      <c r="F6" s="143" t="n">
+        <v>8</v>
+      </c>
+      <c r="G6" s="150" t="s">
+        <v>218</v>
+      </c>
+      <c r="H6" s="143" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="I6" s="145" t="n">
+        <v>2.9046</v>
+      </c>
+      <c r="J6" s="145" t="n">
+        <v>2.9046</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="148" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="148" t="s">
+        <v>219</v>
+      </c>
+      <c r="C7" s="148" t="s">
+        <v>219</v>
+      </c>
+      <c r="D7" s="149" t="s">
+        <v>219</v>
+      </c>
+      <c r="E7" s="148" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="148" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="151" t="s">
+        <v>220</v>
+      </c>
+      <c r="H7" s="143" t="n">
+        <v>0.81</v>
+      </c>
+      <c r="I7" s="145" t="n">
+        <v>1.1421</v>
+      </c>
+      <c r="J7" s="145" t="n">
+        <v>1.1421</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="143" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="143" t="s">
+        <v>221</v>
+      </c>
+      <c r="C8" s="143" t="s">
+        <v>222</v>
+      </c>
+      <c r="D8" s="144" t="s">
+        <v>217</v>
+      </c>
+      <c r="E8" s="143" t="n">
+        <v>8</v>
+      </c>
+      <c r="F8" s="143" t="n">
+        <v>8</v>
+      </c>
+      <c r="G8" s="152" t="s">
+        <v>223</v>
+      </c>
+      <c r="H8" s="143" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I8" s="145" t="n">
+        <v>1.269</v>
+      </c>
+      <c r="J8" s="145" t="n">
+        <v>1.269</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="143" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="143" t="s">
+        <v>224</v>
+      </c>
+      <c r="C9" s="143" t="s">
+        <v>225</v>
+      </c>
+      <c r="D9" s="144" t="s">
+        <v>217</v>
+      </c>
+      <c r="E9" s="143" t="n">
+        <v>8</v>
+      </c>
+      <c r="F9" s="143" t="n">
+        <v>8</v>
+      </c>
+      <c r="G9" s="153" t="s">
+        <v>226</v>
+      </c>
+      <c r="H9" s="144" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="I9" s="145" t="n">
+        <v>2.3688</v>
+      </c>
+      <c r="J9" s="145" t="n">
+        <v>2.3688</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="143" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="143" t="s">
+        <v>224</v>
+      </c>
+      <c r="C10" s="143" t="s">
+        <v>227</v>
+      </c>
+      <c r="D10" s="144" t="s">
+        <v>207</v>
+      </c>
+      <c r="E10" s="143" t="n">
+        <v>8</v>
+      </c>
+      <c r="F10" s="143" t="n">
+        <v>8</v>
+      </c>
+      <c r="G10" s="153" t="s">
+        <v>228</v>
+      </c>
+      <c r="H10" s="144" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="145" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="145" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="144" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="144" t="s">
+        <v>229</v>
+      </c>
+      <c r="C11" s="144" t="s">
+        <v>230</v>
+      </c>
+      <c r="D11" s="144" t="s">
         <v>231</v>
       </c>
-      <c r="B1" s="141" t="s">
+      <c r="E11" s="144" t="n">
+        <v>8</v>
+      </c>
+      <c r="F11" s="144" t="n">
+        <v>8</v>
+      </c>
+      <c r="G11" s="153" t="s">
         <v>232</v>
       </c>
-      <c r="C1" s="141" t="s">
+      <c r="H11" s="144" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="145" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="145" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="148" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="148" t="s">
         <v>233</v>
       </c>
-      <c r="D1" s="142" t="s">
+      <c r="C12" s="148" t="s">
         <v>234</v>
       </c>
-      <c r="E1" s="141" t="s">
+      <c r="D12" s="149" t="s">
+        <v>217</v>
+      </c>
+      <c r="E12" s="148" t="n">
+        <v>8</v>
+      </c>
+      <c r="F12" s="148" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="153" t="s">
         <v>235</v>
       </c>
-      <c r="F1" s="141" t="s">
+      <c r="H12" s="143" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I12" s="145" t="n">
+        <v>1.269</v>
+      </c>
+      <c r="J12" s="145" t="n">
+        <v>1.269</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="143" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="143" t="s">
         <v>236</v>
       </c>
-      <c r="G1" s="142" t="s">
+      <c r="C13" s="143" t="s">
         <v>237</v>
       </c>
-      <c r="H1" s="142" t="s">
+      <c r="D13" s="144" t="s">
+        <v>217</v>
+      </c>
+      <c r="E13" s="143" t="n">
+        <v>8</v>
+      </c>
+      <c r="F13" s="143" t="n">
+        <v>8</v>
+      </c>
+      <c r="G13" s="153" t="s">
         <v>238</v>
       </c>
-      <c r="I1" s="143" t="s">
+      <c r="H13" s="143" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="I13" s="145" t="n">
+        <v>1.6638</v>
+      </c>
+      <c r="J13" s="145" t="n">
+        <v>1.6638</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="143" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" s="143" t="s">
+        <v>236</v>
+      </c>
+      <c r="C14" s="143" t="s">
         <v>239</v>
       </c>
-      <c r="J1" s="143" t="s">
+      <c r="D14" s="144" t="s">
+        <v>207</v>
+      </c>
+      <c r="E14" s="143" t="n">
+        <v>8</v>
+      </c>
+      <c r="F14" s="143" t="n">
+        <v>8</v>
+      </c>
+      <c r="G14" s="153" t="s">
+        <v>238</v>
+      </c>
+      <c r="H14" s="144" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="145" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="145" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="148" t="n">
+        <v>9</v>
+      </c>
+      <c r="B15" s="148" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="141" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="141" t="s">
+      <c r="C15" s="148" t="s">
         <v>241</v>
       </c>
-      <c r="C2" s="141" t="s">
+      <c r="D15" s="149" t="s">
+        <v>217</v>
+      </c>
+      <c r="E15" s="148" t="n">
+        <v>8</v>
+      </c>
+      <c r="F15" s="148" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="153" t="s">
         <v>242</v>
       </c>
-      <c r="D2" s="142" t="s">
+      <c r="H15" s="149" t="n">
+        <v>0.81</v>
+      </c>
+      <c r="I15" s="145" t="n">
+        <v>1.1421</v>
+      </c>
+      <c r="J15" s="145" t="n">
+        <v>1.1421</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="148" t="n">
+        <v>10</v>
+      </c>
+      <c r="B16" s="148" t="s">
         <v>243</v>
       </c>
-      <c r="E2" s="141" t="n">
+      <c r="C16" s="148" t="s">
+        <v>244</v>
+      </c>
+      <c r="D16" s="149" t="s">
+        <v>217</v>
+      </c>
+      <c r="E16" s="148" t="n">
         <v>8</v>
       </c>
-      <c r="F2" s="141" t="n">
-        <v>8</v>
-      </c>
-      <c r="G2" s="144" t="s">
-        <v>244</v>
-      </c>
-      <c r="H2" s="141" t="n">
+      <c r="F16" s="149" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="152" t="s">
+        <v>245</v>
+      </c>
+      <c r="H16" s="149" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="I16" s="145" t="n">
+        <v>1.6638</v>
+      </c>
+      <c r="J16" s="145" t="n">
+        <v>1.6638</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="145"/>
+      <c r="B17" s="145"/>
+      <c r="C17" s="145"/>
+      <c r="D17" s="145"/>
+      <c r="E17" s="145" t="n">
+        <v>112</v>
+      </c>
+      <c r="F17" s="145" t="n">
+        <v>72</v>
+      </c>
+      <c r="G17" s="145"/>
+      <c r="H17" s="145"/>
+      <c r="I17" s="145" t="n">
+        <v>22.9548</v>
+      </c>
+      <c r="J17" s="145"/>
+    </row>
+    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="G20" s="154" t="s">
+        <v>246</v>
+      </c>
+      <c r="H20" s="154" t="n">
+        <v>206.9548</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="G21" s="155" t="s">
+        <v>247</v>
+      </c>
+      <c r="H21" s="155" t="n">
+        <v>22.89</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="156" t="s">
+        <v>199</v>
+      </c>
+      <c r="B22" s="156"/>
+      <c r="C22" s="156"/>
+      <c r="D22" s="156"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="157" t="s">
+        <v>248</v>
+      </c>
+      <c r="B23" s="157" t="s">
+        <v>249</v>
+      </c>
+      <c r="C23" s="157" t="s">
+        <v>250</v>
+      </c>
+      <c r="D23" s="157" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="157" t="s">
+        <v>252</v>
+      </c>
+      <c r="B24" s="157" t="s">
+        <v>253</v>
+      </c>
+      <c r="C24" s="158" t="s">
+        <v>205</v>
+      </c>
+      <c r="D24" s="157" t="n">
         <v>2.35</v>
       </c>
-      <c r="I2" s="143" t="n">
-        <v>3.3135</v>
-      </c>
-      <c r="J2" s="143" t="n">
-        <v>3.3135</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="141" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" s="141" t="s">
-        <v>241</v>
-      </c>
-      <c r="C3" s="145" t="s">
+    </row>
+    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="157" t="s">
+        <v>254</v>
+      </c>
+      <c r="B25" s="157" t="s">
+        <v>209</v>
+      </c>
+      <c r="C25" s="158" t="s">
+        <v>211</v>
+      </c>
+      <c r="D25" s="157" t="n">
+        <v>2.35</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="159" t="s">
+        <v>255</v>
+      </c>
+      <c r="B26" s="159" t="s">
+        <v>215</v>
+      </c>
+      <c r="C26" s="160" t="s">
+        <v>218</v>
+      </c>
+      <c r="D26" s="157" t="n">
+        <v>2.06</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="159"/>
+      <c r="B27" s="159"/>
+      <c r="C27" s="161" t="s">
+        <v>256</v>
+      </c>
+      <c r="D27" s="157" t="n">
+        <v>2.35</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="159" t="s">
+        <v>257</v>
+      </c>
+      <c r="B28" s="159" t="s">
+        <v>258</v>
+      </c>
+      <c r="C28" s="158" t="s">
+        <v>220</v>
+      </c>
+      <c r="D28" s="157" t="n">
+        <v>0.81</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="159"/>
+      <c r="B29" s="159"/>
+      <c r="C29" s="162" t="s">
+        <v>259</v>
+      </c>
+      <c r="D29" s="157" t="n">
+        <v>1.98</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="159" t="s">
+        <v>260</v>
+      </c>
+      <c r="B30" s="159" t="s">
+        <v>261</v>
+      </c>
+      <c r="C30" s="163" t="s">
+        <v>262</v>
+      </c>
+      <c r="D30" s="157" t="n">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="159"/>
+      <c r="B31" s="159"/>
+      <c r="C31" s="157" t="s">
+        <v>223</v>
+      </c>
+      <c r="D31" s="157" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="157" t="s">
+        <v>263</v>
+      </c>
+      <c r="B32" s="157" t="s">
+        <v>224</v>
+      </c>
+      <c r="C32" s="164" t="s">
+        <v>226</v>
+      </c>
+      <c r="D32" s="157" t="n">
+        <v>1.68</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="157" t="s">
+        <v>264</v>
+      </c>
+      <c r="B33" s="157" t="s">
+        <v>265</v>
+      </c>
+      <c r="C33" s="158" t="s">
+        <v>235</v>
+      </c>
+      <c r="D33" s="157" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="157" t="s">
+        <v>266</v>
+      </c>
+      <c r="B34" s="157" t="s">
+        <v>236</v>
+      </c>
+      <c r="C34" s="164" t="s">
+        <v>238</v>
+      </c>
+      <c r="D34" s="157" t="n">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="159" t="s">
+        <v>267</v>
+      </c>
+      <c r="B35" s="159" t="s">
+        <v>240</v>
+      </c>
+      <c r="C35" s="158" t="s">
+        <v>242</v>
+      </c>
+      <c r="D35" s="157" t="n">
+        <v>0.81</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="159"/>
+      <c r="B36" s="159"/>
+      <c r="C36" s="161" t="s">
+        <v>268</v>
+      </c>
+      <c r="D36" s="157" t="n">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="159" t="s">
+        <v>269</v>
+      </c>
+      <c r="B37" s="159" t="s">
+        <v>243</v>
+      </c>
+      <c r="C37" s="163" t="s">
+        <v>270</v>
+      </c>
+      <c r="D37" s="157" t="n">
+        <v>1.98</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="159"/>
+      <c r="B38" s="159"/>
+      <c r="C38" s="157" t="s">
         <v>245</v>
       </c>
-      <c r="D3" s="142" t="s">
-        <v>246</v>
-      </c>
-      <c r="E3" s="141" t="n">
-        <v>8</v>
-      </c>
-      <c r="F3" s="141" t="n">
-        <v>8</v>
-      </c>
-      <c r="G3" s="144" t="s">
-        <v>247</v>
-      </c>
-      <c r="H3" s="141" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="I3" s="143" t="n">
-        <v>3.3135</v>
-      </c>
-      <c r="J3" s="143" t="n">
-        <v>3.3135</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="146" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" s="146" t="s">
-        <v>248</v>
-      </c>
-      <c r="C4" s="146" t="s">
-        <v>249</v>
-      </c>
-      <c r="D4" s="147" t="s">
-        <v>243</v>
-      </c>
-      <c r="E4" s="146" t="n">
-        <v>8</v>
-      </c>
-      <c r="F4" s="146" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="148" t="s">
-        <v>250</v>
-      </c>
-      <c r="H4" s="141" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="I4" s="143" t="n">
-        <v>2.9046</v>
-      </c>
-      <c r="J4" s="143" t="n">
-        <v>2.9046</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="147" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="147" t="s">
-        <v>248</v>
-      </c>
-      <c r="C5" s="146" t="s">
-        <v>251</v>
-      </c>
-      <c r="D5" s="147" t="s">
-        <v>252</v>
-      </c>
-      <c r="E5" s="147" t="n">
-        <v>8</v>
-      </c>
-      <c r="F5" s="147" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="148" t="s">
-        <v>253</v>
-      </c>
-      <c r="H5" s="142" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="143" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="143" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="141" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="141" t="s">
-        <v>254</v>
-      </c>
-      <c r="C6" s="141" t="s">
-        <v>255</v>
-      </c>
-      <c r="D6" s="142" t="s">
-        <v>256</v>
-      </c>
-      <c r="E6" s="141" t="n">
-        <v>8</v>
-      </c>
-      <c r="F6" s="141" t="n">
-        <v>8</v>
-      </c>
-      <c r="G6" s="148" t="s">
-        <v>257</v>
-      </c>
-      <c r="H6" s="141" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="I6" s="143" t="n">
-        <v>2.9046</v>
-      </c>
-      <c r="J6" s="143" t="n">
-        <v>2.9046</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="146" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="146" t="s">
-        <v>258</v>
-      </c>
-      <c r="C7" s="146" t="s">
-        <v>258</v>
-      </c>
-      <c r="D7" s="147" t="s">
-        <v>258</v>
-      </c>
-      <c r="E7" s="146" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="146" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="149" t="s">
-        <v>259</v>
-      </c>
-      <c r="H7" s="141" t="n">
-        <v>0.81</v>
-      </c>
-      <c r="I7" s="143" t="n">
-        <v>1.1421</v>
-      </c>
-      <c r="J7" s="143" t="n">
-        <v>1.1421</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="141" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="141" t="s">
-        <v>260</v>
-      </c>
-      <c r="C8" s="141" t="s">
-        <v>261</v>
-      </c>
-      <c r="D8" s="142" t="s">
-        <v>256</v>
-      </c>
-      <c r="E8" s="141" t="n">
-        <v>8</v>
-      </c>
-      <c r="F8" s="141" t="n">
-        <v>8</v>
-      </c>
-      <c r="G8" s="150" t="s">
-        <v>262</v>
-      </c>
-      <c r="H8" s="141" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="I8" s="143" t="n">
-        <v>1.269</v>
-      </c>
-      <c r="J8" s="143" t="n">
-        <v>1.269</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="141" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="141" t="s">
-        <v>263</v>
-      </c>
-      <c r="C9" s="141" t="s">
-        <v>264</v>
-      </c>
-      <c r="D9" s="142" t="s">
-        <v>256</v>
-      </c>
-      <c r="E9" s="141" t="n">
-        <v>8</v>
-      </c>
-      <c r="F9" s="141" t="n">
-        <v>8</v>
-      </c>
-      <c r="G9" s="151" t="s">
-        <v>265</v>
-      </c>
-      <c r="H9" s="142" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="I9" s="143" t="n">
-        <v>2.3688</v>
-      </c>
-      <c r="J9" s="143" t="n">
-        <v>2.3688</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="141" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="141" t="s">
-        <v>263</v>
-      </c>
-      <c r="C10" s="141" t="s">
-        <v>266</v>
-      </c>
-      <c r="D10" s="142" t="s">
-        <v>246</v>
-      </c>
-      <c r="E10" s="141" t="n">
-        <v>8</v>
-      </c>
-      <c r="F10" s="141" t="n">
-        <v>8</v>
-      </c>
-      <c r="G10" s="151" t="s">
-        <v>267</v>
-      </c>
-      <c r="H10" s="142" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="143" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="143" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="142" t="n">
-        <v>6</v>
-      </c>
-      <c r="B11" s="142" t="s">
-        <v>268</v>
-      </c>
-      <c r="C11" s="142" t="s">
-        <v>269</v>
-      </c>
-      <c r="D11" s="142" t="s">
-        <v>270</v>
-      </c>
-      <c r="E11" s="142" t="n">
-        <v>8</v>
-      </c>
-      <c r="F11" s="142" t="n">
-        <v>8</v>
-      </c>
-      <c r="G11" s="151" t="s">
-        <v>271</v>
-      </c>
-      <c r="H11" s="142" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="143" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="143" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="146" t="n">
-        <v>7</v>
-      </c>
-      <c r="B12" s="146" t="s">
-        <v>272</v>
-      </c>
-      <c r="C12" s="146" t="s">
-        <v>273</v>
-      </c>
-      <c r="D12" s="147" t="s">
-        <v>256</v>
-      </c>
-      <c r="E12" s="146" t="n">
-        <v>8</v>
-      </c>
-      <c r="F12" s="146" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="151" t="s">
-        <v>274</v>
-      </c>
-      <c r="H12" s="141" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="I12" s="143" t="n">
-        <v>1.269</v>
-      </c>
-      <c r="J12" s="143" t="n">
-        <v>1.269</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="141" t="n">
-        <v>8</v>
-      </c>
-      <c r="B13" s="141" t="s">
-        <v>275</v>
-      </c>
-      <c r="C13" s="141" t="s">
-        <v>276</v>
-      </c>
-      <c r="D13" s="142" t="s">
-        <v>256</v>
-      </c>
-      <c r="E13" s="141" t="n">
-        <v>8</v>
-      </c>
-      <c r="F13" s="141" t="n">
-        <v>8</v>
-      </c>
-      <c r="G13" s="151" t="s">
-        <v>277</v>
-      </c>
-      <c r="H13" s="141" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="I13" s="143" t="n">
-        <v>1.6638</v>
-      </c>
-      <c r="J13" s="143" t="n">
-        <v>1.6638</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="141" t="n">
-        <v>8</v>
-      </c>
-      <c r="B14" s="141" t="s">
-        <v>275</v>
-      </c>
-      <c r="C14" s="141" t="s">
-        <v>278</v>
-      </c>
-      <c r="D14" s="142" t="s">
-        <v>246</v>
-      </c>
-      <c r="E14" s="141" t="n">
-        <v>8</v>
-      </c>
-      <c r="F14" s="141" t="n">
-        <v>8</v>
-      </c>
-      <c r="G14" s="151" t="s">
-        <v>277</v>
-      </c>
-      <c r="H14" s="142" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="143" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="143" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="146" t="n">
-        <v>9</v>
-      </c>
-      <c r="B15" s="146" t="s">
-        <v>279</v>
-      </c>
-      <c r="C15" s="146" t="s">
-        <v>280</v>
-      </c>
-      <c r="D15" s="147" t="s">
-        <v>256</v>
-      </c>
-      <c r="E15" s="146" t="n">
-        <v>8</v>
-      </c>
-      <c r="F15" s="146" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="151" t="s">
-        <v>281</v>
-      </c>
-      <c r="H15" s="147" t="n">
-        <v>0.81</v>
-      </c>
-      <c r="I15" s="143" t="n">
-        <v>1.1421</v>
-      </c>
-      <c r="J15" s="143" t="n">
-        <v>1.1421</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="146" t="n">
-        <v>10</v>
-      </c>
-      <c r="B16" s="146" t="s">
-        <v>282</v>
-      </c>
-      <c r="C16" s="146" t="s">
-        <v>283</v>
-      </c>
-      <c r="D16" s="147" t="s">
-        <v>256</v>
-      </c>
-      <c r="E16" s="146" t="n">
-        <v>8</v>
-      </c>
-      <c r="F16" s="147" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="150" t="s">
-        <v>284</v>
-      </c>
-      <c r="H16" s="147" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="I16" s="143" t="n">
-        <v>1.6638</v>
-      </c>
-      <c r="J16" s="143" t="n">
-        <v>1.6638</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="143"/>
-      <c r="B17" s="143"/>
-      <c r="C17" s="143"/>
-      <c r="D17" s="143"/>
-      <c r="E17" s="143" t="n">
-        <v>112</v>
-      </c>
-      <c r="F17" s="143" t="n">
-        <v>72</v>
-      </c>
-      <c r="G17" s="143"/>
-      <c r="H17" s="143"/>
-      <c r="I17" s="143" t="n">
-        <v>22.9548</v>
-      </c>
-      <c r="J17" s="143"/>
-    </row>
-    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G20" s="152" t="s">
-        <v>285</v>
-      </c>
-      <c r="H20" s="152" t="n">
-        <v>206.9548</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="G21" s="153" t="s">
-        <v>286</v>
-      </c>
-      <c r="H21" s="153" t="n">
-        <v>22.89</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="154" t="s">
-        <v>238</v>
-      </c>
-      <c r="B22" s="154"/>
-      <c r="C22" s="154"/>
-      <c r="D22" s="154"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="155" t="s">
-        <v>287</v>
-      </c>
-      <c r="B23" s="155" t="s">
-        <v>288</v>
-      </c>
-      <c r="C23" s="155" t="s">
-        <v>289</v>
-      </c>
-      <c r="D23" s="155" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="155" t="s">
-        <v>291</v>
-      </c>
-      <c r="B24" s="155" t="s">
-        <v>292</v>
-      </c>
-      <c r="C24" s="156" t="s">
-        <v>244</v>
-      </c>
-      <c r="D24" s="155" t="n">
-        <v>2.35</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="155" t="s">
-        <v>293</v>
-      </c>
-      <c r="B25" s="155" t="s">
-        <v>248</v>
-      </c>
-      <c r="C25" s="156" t="s">
-        <v>250</v>
-      </c>
-      <c r="D25" s="155" t="n">
-        <v>2.35</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="157" t="s">
-        <v>294</v>
-      </c>
-      <c r="B26" s="157" t="s">
-        <v>254</v>
-      </c>
-      <c r="C26" s="158" t="s">
-        <v>257</v>
-      </c>
-      <c r="D26" s="155" t="n">
-        <v>2.06</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="157"/>
-      <c r="B27" s="157"/>
-      <c r="C27" s="159" t="s">
-        <v>295</v>
-      </c>
-      <c r="D27" s="155" t="n">
-        <v>2.35</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="157" t="s">
-        <v>296</v>
-      </c>
-      <c r="B28" s="157" t="s">
-        <v>297</v>
-      </c>
-      <c r="C28" s="156" t="s">
-        <v>259</v>
-      </c>
-      <c r="D28" s="155" t="n">
-        <v>0.81</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="157"/>
-      <c r="B29" s="157"/>
-      <c r="C29" s="160" t="s">
-        <v>298</v>
-      </c>
-      <c r="D29" s="155" t="n">
-        <v>1.98</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="157" t="s">
-        <v>299</v>
-      </c>
-      <c r="B30" s="157" t="s">
-        <v>300</v>
-      </c>
-      <c r="C30" s="161" t="s">
-        <v>301</v>
-      </c>
-      <c r="D30" s="155" t="n">
-        <v>1.18</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="157"/>
-      <c r="B31" s="157"/>
-      <c r="C31" s="155" t="s">
-        <v>262</v>
-      </c>
-      <c r="D31" s="155" t="n">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="155" t="s">
-        <v>302</v>
-      </c>
-      <c r="B32" s="155" t="s">
-        <v>263</v>
-      </c>
-      <c r="C32" s="162" t="s">
-        <v>265</v>
-      </c>
-      <c r="D32" s="155" t="n">
-        <v>1.68</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="155" t="s">
-        <v>303</v>
-      </c>
-      <c r="B33" s="155" t="s">
-        <v>304</v>
-      </c>
-      <c r="C33" s="156" t="s">
-        <v>274</v>
-      </c>
-      <c r="D33" s="155" t="n">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="155" t="s">
-        <v>305</v>
-      </c>
-      <c r="B34" s="155" t="s">
-        <v>275</v>
-      </c>
-      <c r="C34" s="162" t="s">
-        <v>277</v>
-      </c>
-      <c r="D34" s="155" t="n">
-        <v>1.18</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="157" t="s">
-        <v>306</v>
-      </c>
-      <c r="B35" s="157" t="s">
-        <v>279</v>
-      </c>
-      <c r="C35" s="156" t="s">
-        <v>281</v>
-      </c>
-      <c r="D35" s="155" t="n">
-        <v>0.81</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="157"/>
-      <c r="B36" s="157"/>
-      <c r="C36" s="159" t="s">
-        <v>307</v>
-      </c>
-      <c r="D36" s="155" t="n">
-        <v>1.18</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="157" t="s">
-        <v>308</v>
-      </c>
-      <c r="B37" s="157" t="s">
-        <v>282</v>
-      </c>
-      <c r="C37" s="161" t="s">
-        <v>309</v>
-      </c>
-      <c r="D37" s="155" t="n">
-        <v>1.98</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="157"/>
-      <c r="B38" s="157"/>
-      <c r="C38" s="155" t="s">
-        <v>284</v>
-      </c>
-      <c r="D38" s="155" t="n">
+      <c r="D38" s="157" t="n">
         <v>1.18</v>
       </c>
     </row>
@@ -10623,15 +10521,15 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="143"/>
-      <c r="B1" s="143" t="s">
-        <v>310</v>
-      </c>
-      <c r="C1" s="143" t="s">
-        <v>311</v>
-      </c>
-      <c r="D1" s="163" t="s">
-        <v>312</v>
+      <c r="A1" s="145"/>
+      <c r="B1" s="145" t="s">
+        <v>271</v>
+      </c>
+      <c r="C1" s="145" t="s">
+        <v>272</v>
+      </c>
+      <c r="D1" s="165" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10639,10 +10537,10 @@
         <v>28</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C2" s="14"/>
-      <c r="D2" s="164"/>
+      <c r="D2" s="166"/>
       <c r="E2" s="1" t="n">
         <v>1</v>
       </c>
@@ -10656,7 +10554,7 @@
       </c>
       <c r="B3" s="16"/>
       <c r="C3" s="14"/>
-      <c r="D3" s="164"/>
+      <c r="D3" s="166"/>
       <c r="E3" s="1" t="n">
         <v>2</v>
       </c>
@@ -10669,13 +10567,13 @@
         <v>31</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="D4" s="164" t="s">
-        <v>69</v>
+        <v>68</v>
+      </c>
+      <c r="D4" s="166" t="s">
+        <v>68</v>
       </c>
       <c r="E4" s="1" t="n">
         <v>3</v>
@@ -10686,16 +10584,16 @@
     </row>
     <row r="5" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>313</v>
+        <v>274</v>
       </c>
       <c r="B5" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="C5" s="167" t="s">
         <v>69</v>
       </c>
-      <c r="C5" s="165" t="s">
-        <v>70</v>
-      </c>
-      <c r="D5" s="166" t="s">
-        <v>70</v>
+      <c r="D5" s="168" t="s">
+        <v>69</v>
       </c>
       <c r="E5" s="1" t="n">
         <v>4</v>
@@ -10706,16 +10604,16 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>314</v>
+        <v>275</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="D6" s="164" t="s">
-        <v>69</v>
+        <v>68</v>
+      </c>
+      <c r="D6" s="166" t="s">
+        <v>68</v>
       </c>
       <c r="E6" s="1" t="n">
         <v>5</v>
@@ -10726,14 +10624,14 @@
     </row>
     <row r="7" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>315</v>
-      </c>
-      <c r="B7" s="167"/>
-      <c r="C7" s="165" t="s">
-        <v>62</v>
-      </c>
-      <c r="D7" s="166" t="s">
-        <v>62</v>
+        <v>276</v>
+      </c>
+      <c r="B7" s="169"/>
+      <c r="C7" s="167" t="s">
+        <v>61</v>
+      </c>
+      <c r="D7" s="168" t="s">
+        <v>61</v>
       </c>
       <c r="E7" s="1" t="n">
         <v>6</v>
@@ -10744,13 +10642,13 @@
     </row>
     <row r="8" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>316</v>
+        <v>277</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>317</v>
-      </c>
-      <c r="C8" s="165"/>
-      <c r="D8" s="166"/>
+        <v>278</v>
+      </c>
+      <c r="C8" s="167"/>
+      <c r="D8" s="168"/>
       <c r="E8" s="1" t="n">
         <v>7</v>
       </c>
@@ -10760,16 +10658,16 @@
     </row>
     <row r="9" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>318</v>
+        <v>279</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>317</v>
-      </c>
-      <c r="C9" s="165" t="s">
-        <v>70</v>
-      </c>
-      <c r="D9" s="166" t="s">
-        <v>70</v>
+        <v>278</v>
+      </c>
+      <c r="C9" s="167" t="s">
+        <v>69</v>
+      </c>
+      <c r="D9" s="168" t="s">
+        <v>69</v>
       </c>
       <c r="E9" s="1" t="n">
         <v>8</v>
@@ -10780,14 +10678,14 @@
     </row>
     <row r="10" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>319</v>
+        <v>280</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>317</v>
-      </c>
-      <c r="C10" s="165"/>
-      <c r="D10" s="166" t="s">
-        <v>69</v>
+        <v>278</v>
+      </c>
+      <c r="C10" s="167"/>
+      <c r="D10" s="168" t="s">
+        <v>68</v>
       </c>
       <c r="E10" s="1" t="n">
         <v>9</v>
@@ -10798,13 +10696,13 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>320</v>
-      </c>
-      <c r="B11" s="167" t="s">
-        <v>317</v>
-      </c>
-      <c r="C11" s="165"/>
-      <c r="D11" s="166"/>
+        <v>281</v>
+      </c>
+      <c r="B11" s="169" t="s">
+        <v>278</v>
+      </c>
+      <c r="C11" s="167"/>
+      <c r="D11" s="168"/>
       <c r="E11" s="1" t="n">
         <v>10</v>
       </c>
@@ -10814,12 +10712,12 @@
     </row>
     <row r="12" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="B12" s="167"/>
-      <c r="C12" s="165"/>
-      <c r="D12" s="166" t="s">
-        <v>69</v>
+        <v>282</v>
+      </c>
+      <c r="B12" s="169"/>
+      <c r="C12" s="167"/>
+      <c r="D12" s="168" t="s">
+        <v>68</v>
       </c>
       <c r="E12" s="1" t="n">
         <v>11</v>
@@ -10830,14 +10728,14 @@
     </row>
     <row r="13" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>321</v>
-      </c>
-      <c r="B13" s="167" t="s">
-        <v>317</v>
-      </c>
-      <c r="C13" s="165"/>
-      <c r="D13" s="166" t="s">
-        <v>317</v>
+        <v>283</v>
+      </c>
+      <c r="B13" s="169" t="s">
+        <v>278</v>
+      </c>
+      <c r="C13" s="167"/>
+      <c r="D13" s="168" t="s">
+        <v>278</v>
       </c>
       <c r="E13" s="1" t="n">
         <v>12</v>
@@ -10848,12 +10746,12 @@
     </row>
     <row r="14" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="28" t="s">
-        <v>144</v>
+        <v>284</v>
       </c>
       <c r="B14" s="32"/>
       <c r="C14" s="30"/>
-      <c r="D14" s="168" t="s">
-        <v>70</v>
+      <c r="D14" s="170" t="s">
+        <v>69</v>
       </c>
       <c r="E14" s="1" t="n">
         <v>13</v>
@@ -10884,51 +10782,51 @@
       <c r="D18" s="2"/>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="169"/>
-      <c r="C19" s="170"/>
-      <c r="D19" s="170"/>
+      <c r="B19" s="171"/>
+      <c r="C19" s="172"/>
+      <c r="D19" s="172"/>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="171"/>
-      <c r="C20" s="171"/>
-      <c r="D20" s="171"/>
+      <c r="B20" s="173"/>
+      <c r="C20" s="173"/>
+      <c r="D20" s="173"/>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="172"/>
-      <c r="C21" s="116"/>
-      <c r="D21" s="171"/>
+      <c r="B21" s="174"/>
+      <c r="C21" s="118"/>
+      <c r="D21" s="173"/>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="172"/>
-      <c r="C22" s="116"/>
-      <c r="D22" s="171"/>
+      <c r="B22" s="174"/>
+      <c r="C22" s="118"/>
+      <c r="D22" s="173"/>
     </row>
     <row r="23" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="173" t="s">
-        <v>136</v>
+      <c r="B23" s="175" t="s">
+        <v>285</v>
       </c>
       <c r="C23" s="77"/>
-      <c r="D23" s="116"/>
+      <c r="D23" s="118"/>
     </row>
     <row r="24" customFormat="false" ht="52.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="119" t="s">
-        <v>139</v>
+      <c r="B24" s="121" t="s">
+        <v>286</v>
       </c>
       <c r="C24" s="77"/>
-      <c r="D24" s="116"/>
+      <c r="D24" s="118"/>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="172"/>
+      <c r="B25" s="174"/>
       <c r="C25" s="77"/>
-      <c r="D25" s="172"/>
+      <c r="D25" s="174"/>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="172"/>
+      <c r="B26" s="174"/>
       <c r="C26" s="77"/>
-      <c r="D26" s="116"/>
+      <c r="D26" s="118"/>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="172"/>
+      <c r="B27" s="174"/>
       <c r="C27" s="77"/>
       <c r="D27" s="77"/>
     </row>
@@ -10961,16 +10859,16 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="174" t="s">
-        <v>322</v>
-      </c>
-      <c r="B1" s="174" t="s">
-        <v>323</v>
-      </c>
-      <c r="C1" s="174" t="s">
-        <v>324</v>
-      </c>
-      <c r="D1" s="174" t="s">
+      <c r="A1" s="176" t="s">
+        <v>287</v>
+      </c>
+      <c r="B1" s="176" t="s">
+        <v>288</v>
+      </c>
+      <c r="C1" s="176" t="s">
+        <v>289</v>
+      </c>
+      <c r="D1" s="176" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="3" t="s">
@@ -10987,14 +10885,14 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="174" t="s">
-        <v>325</v>
-      </c>
-      <c r="B2" s="174" t="s">
-        <v>326</v>
+      <c r="A2" s="176" t="s">
+        <v>290</v>
+      </c>
+      <c r="B2" s="176" t="s">
+        <v>291</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>327</v>
+        <v>292</v>
       </c>
       <c r="D2" s="11" t="n">
         <v>1</v>
@@ -11008,15 +10906,15 @@
       <c r="H2" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="I2" s="175" t="s">
-        <v>62</v>
+      <c r="I2" s="177" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="174"/>
-      <c r="B3" s="174"/>
-      <c r="C3" s="174"/>
-      <c r="D3" s="174"/>
+      <c r="A3" s="176"/>
+      <c r="B3" s="176"/>
+      <c r="C3" s="176"/>
+      <c r="D3" s="176"/>
       <c r="F3" s="10"/>
       <c r="G3" s="11" t="s">
         <v>17</v>
@@ -11024,15 +10922,15 @@
       <c r="H3" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="I3" s="176" t="s">
-        <v>62</v>
+      <c r="I3" s="178" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="174"/>
-      <c r="B4" s="174"/>
-      <c r="C4" s="174"/>
-      <c r="D4" s="174"/>
+      <c r="A4" s="176"/>
+      <c r="B4" s="176"/>
+      <c r="C4" s="176"/>
+      <c r="D4" s="176"/>
       <c r="F4" s="10"/>
       <c r="G4" s="11" t="s">
         <v>19</v>
@@ -11040,15 +10938,15 @@
       <c r="H4" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="I4" s="176" t="s">
-        <v>62</v>
+      <c r="I4" s="178" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="174"/>
-      <c r="B5" s="174"/>
-      <c r="C5" s="174"/>
-      <c r="D5" s="174"/>
+      <c r="A5" s="176"/>
+      <c r="B5" s="176"/>
+      <c r="C5" s="176"/>
+      <c r="D5" s="176"/>
       <c r="F5" s="10"/>
       <c r="G5" s="11" t="s">
         <v>21</v>
@@ -11056,13 +10954,13 @@
       <c r="H5" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="I5" s="176" t="s">
-        <v>62</v>
+      <c r="I5" s="178" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="174"/>
-      <c r="B6" s="174"/>
+      <c r="A6" s="176"/>
+      <c r="B6" s="176"/>
       <c r="C6" s="11"/>
       <c r="D6" s="11"/>
       <c r="F6" s="10"/>
@@ -11072,15 +10970,15 @@
       <c r="H6" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="I6" s="176" t="s">
-        <v>62</v>
+      <c r="I6" s="178" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="174"/>
-      <c r="B7" s="174"/>
+      <c r="A7" s="176"/>
+      <c r="B7" s="176"/>
       <c r="C7" s="11" t="s">
-        <v>328</v>
+        <v>293</v>
       </c>
       <c r="D7" s="11" t="n">
         <v>2</v>
@@ -11092,15 +10990,15 @@
       <c r="H7" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="I7" s="176" t="s">
-        <v>61</v>
+      <c r="I7" s="178" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="174"/>
-      <c r="B8" s="174"/>
-      <c r="C8" s="174"/>
-      <c r="D8" s="174"/>
+      <c r="A8" s="176"/>
+      <c r="B8" s="176"/>
+      <c r="C8" s="176"/>
+      <c r="D8" s="176"/>
       <c r="F8" s="10"/>
       <c r="G8" s="11" t="s">
         <v>26</v>
@@ -11108,19 +11006,19 @@
       <c r="H8" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="I8" s="176" t="s">
-        <v>61</v>
+      <c r="I8" s="178" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="177" t="s">
-        <v>254</v>
-      </c>
-      <c r="B9" s="177" t="s">
-        <v>329</v>
+      <c r="A9" s="179" t="s">
+        <v>215</v>
+      </c>
+      <c r="B9" s="179" t="s">
+        <v>294</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>330</v>
+        <v>295</v>
       </c>
       <c r="D9" s="11" t="n">
         <v>3</v>
@@ -11132,15 +11030,15 @@
       <c r="H9" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="I9" s="176" t="s">
-        <v>61</v>
+      <c r="I9" s="178" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="177"/>
-      <c r="B10" s="177"/>
-      <c r="C10" s="177"/>
-      <c r="D10" s="177"/>
+      <c r="A10" s="179"/>
+      <c r="B10" s="179"/>
+      <c r="C10" s="179"/>
+      <c r="D10" s="179"/>
       <c r="F10" s="10"/>
       <c r="G10" s="11" t="s">
         <v>28</v>
@@ -11148,15 +11046,15 @@
       <c r="H10" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="I10" s="176" t="s">
-        <v>61</v>
+      <c r="I10" s="178" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="177"/>
-      <c r="B11" s="177"/>
-      <c r="C11" s="177"/>
-      <c r="D11" s="177"/>
+      <c r="A11" s="179"/>
+      <c r="B11" s="179"/>
+      <c r="C11" s="179"/>
+      <c r="D11" s="179"/>
       <c r="F11" s="10" t="n">
         <v>2</v>
       </c>
@@ -11166,15 +11064,15 @@
       <c r="H11" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="I11" s="178" t="s">
-        <v>69</v>
+      <c r="I11" s="180" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="177"/>
-      <c r="B12" s="177"/>
-      <c r="C12" s="177"/>
-      <c r="D12" s="177"/>
+      <c r="A12" s="179"/>
+      <c r="B12" s="179"/>
+      <c r="C12" s="179"/>
+      <c r="D12" s="179"/>
       <c r="F12" s="10"/>
       <c r="G12" s="11" t="s">
         <v>31</v>
@@ -11182,15 +11080,15 @@
       <c r="H12" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="I12" s="178" t="s">
-        <v>69</v>
+      <c r="I12" s="180" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="177"/>
-      <c r="B13" s="177"/>
-      <c r="C13" s="177"/>
-      <c r="D13" s="177"/>
+      <c r="A13" s="179"/>
+      <c r="B13" s="179"/>
+      <c r="C13" s="179"/>
+      <c r="D13" s="179"/>
       <c r="F13" s="10" t="n">
         <v>3</v>
       </c>
@@ -11200,13 +11098,13 @@
       <c r="H13" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="I13" s="176" t="s">
-        <v>62</v>
+      <c r="I13" s="178" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="177"/>
-      <c r="B14" s="177"/>
+      <c r="A14" s="179"/>
+      <c r="B14" s="179"/>
       <c r="C14" s="11"/>
       <c r="D14" s="11"/>
       <c r="F14" s="10"/>
@@ -11216,15 +11114,15 @@
       <c r="H14" s="10" t="n">
         <v>13</v>
       </c>
-      <c r="I14" s="178" t="s">
-        <v>69</v>
+      <c r="I14" s="180" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="177"/>
-      <c r="B15" s="177"/>
-      <c r="C15" s="174" t="s">
-        <v>331</v>
+      <c r="A15" s="179"/>
+      <c r="B15" s="179"/>
+      <c r="C15" s="176" t="s">
+        <v>296</v>
       </c>
       <c r="D15" s="11" t="n">
         <v>4</v>
@@ -11236,17 +11134,17 @@
       <c r="H15" s="10" t="n">
         <v>14</v>
       </c>
-      <c r="I15" s="176" t="s">
-        <v>70</v>
+      <c r="I15" s="178" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="177"/>
-      <c r="B16" s="177"/>
-      <c r="C16" s="179" t="s">
-        <v>332</v>
-      </c>
-      <c r="D16" s="180" t="n">
+      <c r="A16" s="179"/>
+      <c r="B16" s="179"/>
+      <c r="C16" s="181" t="s">
+        <v>297</v>
+      </c>
+      <c r="D16" s="182" t="n">
         <v>5</v>
       </c>
       <c r="F16" s="10"/>
@@ -11256,15 +11154,15 @@
       <c r="H16" s="10" t="n">
         <v>15</v>
       </c>
-      <c r="I16" s="178" t="s">
-        <v>61</v>
+      <c r="I16" s="180" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="177"/>
-      <c r="B17" s="177"/>
-      <c r="C17" s="177"/>
-      <c r="D17" s="177"/>
+      <c r="A17" s="179"/>
+      <c r="B17" s="179"/>
+      <c r="C17" s="179"/>
+      <c r="D17" s="179"/>
       <c r="F17" s="10"/>
       <c r="G17" s="11" t="s">
         <v>37</v>
@@ -11272,19 +11170,19 @@
       <c r="H17" s="10" t="n">
         <v>16</v>
       </c>
-      <c r="I17" s="178" t="s">
-        <v>69</v>
+      <c r="I17" s="180" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="174" t="s">
-        <v>263</v>
-      </c>
-      <c r="B18" s="174" t="s">
-        <v>333</v>
-      </c>
-      <c r="C18" s="181" t="s">
-        <v>334</v>
+      <c r="A18" s="176" t="s">
+        <v>224</v>
+      </c>
+      <c r="B18" s="176" t="s">
+        <v>298</v>
+      </c>
+      <c r="C18" s="183" t="s">
+        <v>299</v>
       </c>
       <c r="D18" s="11" t="n">
         <v>6</v>
@@ -11296,15 +11194,15 @@
       <c r="H18" s="10" t="n">
         <v>17</v>
       </c>
-      <c r="I18" s="176" t="s">
-        <v>62</v>
+      <c r="I18" s="178" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="174"/>
-      <c r="B19" s="174"/>
-      <c r="C19" s="174"/>
-      <c r="D19" s="174"/>
+      <c r="A19" s="176"/>
+      <c r="B19" s="176"/>
+      <c r="C19" s="176"/>
+      <c r="D19" s="176"/>
       <c r="F19" s="10" t="n">
         <v>4</v>
       </c>
@@ -11314,15 +11212,15 @@
       <c r="H19" s="10" t="n">
         <v>18</v>
       </c>
-      <c r="I19" s="178" t="s">
-        <v>69</v>
+      <c r="I19" s="180" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="174"/>
-      <c r="B20" s="174"/>
-      <c r="C20" s="174"/>
-      <c r="D20" s="174"/>
+      <c r="A20" s="176"/>
+      <c r="B20" s="176"/>
+      <c r="C20" s="176"/>
+      <c r="D20" s="176"/>
       <c r="F20" s="10"/>
       <c r="G20" s="11" t="s">
         <v>40</v>
@@ -11330,15 +11228,15 @@
       <c r="H20" s="10" t="n">
         <v>19</v>
       </c>
-      <c r="I20" s="176" t="s">
-        <v>62</v>
+      <c r="I20" s="178" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="174"/>
-      <c r="B21" s="174"/>
-      <c r="C21" s="174"/>
-      <c r="D21" s="174"/>
+      <c r="A21" s="176"/>
+      <c r="B21" s="176"/>
+      <c r="C21" s="176"/>
+      <c r="D21" s="176"/>
       <c r="F21" s="10" t="n">
         <v>5</v>
       </c>
@@ -11348,15 +11246,15 @@
       <c r="H21" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="I21" s="178" t="s">
-        <v>69</v>
+      <c r="I21" s="180" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="174"/>
-      <c r="B22" s="174"/>
-      <c r="C22" s="174"/>
-      <c r="D22" s="174"/>
+      <c r="A22" s="176"/>
+      <c r="B22" s="176"/>
+      <c r="C22" s="176"/>
+      <c r="D22" s="176"/>
       <c r="F22" s="10" t="n">
         <v>6</v>
       </c>
@@ -11366,15 +11264,15 @@
       <c r="H22" s="10" t="n">
         <v>21</v>
       </c>
-      <c r="I22" s="176" t="s">
-        <v>69</v>
+      <c r="I22" s="178" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="174"/>
-      <c r="B23" s="174"/>
-      <c r="C23" s="174"/>
-      <c r="D23" s="174"/>
+      <c r="A23" s="176"/>
+      <c r="B23" s="176"/>
+      <c r="C23" s="176"/>
+      <c r="D23" s="176"/>
       <c r="F23" s="10"/>
       <c r="G23" s="11" t="s">
         <v>44</v>
@@ -11382,15 +11280,15 @@
       <c r="H23" s="10" t="n">
         <v>22</v>
       </c>
-      <c r="I23" s="178" t="s">
-        <v>62</v>
+      <c r="I23" s="180" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="174"/>
-      <c r="B24" s="174"/>
-      <c r="C24" s="181"/>
-      <c r="D24" s="181"/>
+      <c r="A24" s="176"/>
+      <c r="B24" s="176"/>
+      <c r="C24" s="183"/>
+      <c r="D24" s="183"/>
       <c r="F24" s="10"/>
       <c r="G24" s="11" t="s">
         <v>45</v>
@@ -11398,15 +11296,15 @@
       <c r="H24" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="I24" s="178" t="s">
-        <v>62</v>
+      <c r="I24" s="180" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="174"/>
-      <c r="B25" s="174"/>
+      <c r="A25" s="176"/>
+      <c r="B25" s="176"/>
       <c r="C25" s="11" t="s">
-        <v>335</v>
+        <v>300</v>
       </c>
       <c r="D25" s="11" t="n">
         <v>7</v>
@@ -11418,13 +11316,13 @@
       <c r="H25" s="10" t="n">
         <v>24</v>
       </c>
-      <c r="I25" s="176" t="s">
-        <v>61</v>
+      <c r="I25" s="178" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="174"/>
-      <c r="B26" s="174"/>
+      <c r="A26" s="176"/>
+      <c r="B26" s="176"/>
       <c r="C26" s="11"/>
       <c r="D26" s="11"/>
       <c r="F26" s="10"/>
@@ -11434,15 +11332,15 @@
       <c r="H26" s="10" t="n">
         <v>25</v>
       </c>
-      <c r="I26" s="176" t="s">
-        <v>62</v>
+      <c r="I26" s="178" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="174"/>
-      <c r="B27" s="174"/>
+      <c r="A27" s="176"/>
+      <c r="B27" s="176"/>
       <c r="C27" s="11" t="s">
-        <v>336</v>
+        <v>301</v>
       </c>
       <c r="D27" s="11" t="n">
         <v>8</v>
@@ -11454,15 +11352,15 @@
       <c r="H27" s="10" t="n">
         <v>26</v>
       </c>
-      <c r="I27" s="178" t="s">
-        <v>69</v>
+      <c r="I27" s="180" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="174"/>
-      <c r="B28" s="174"/>
-      <c r="C28" s="174"/>
-      <c r="D28" s="174"/>
+      <c r="A28" s="176"/>
+      <c r="B28" s="176"/>
+      <c r="C28" s="176"/>
+      <c r="D28" s="176"/>
       <c r="F28" s="10"/>
       <c r="G28" s="11" t="s">
         <v>49</v>
@@ -11470,21 +11368,21 @@
       <c r="H28" s="10" t="n">
         <v>27</v>
       </c>
-      <c r="I28" s="178" t="s">
-        <v>69</v>
+      <c r="I28" s="180" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="44.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="182" t="s">
-        <v>300</v>
-      </c>
-      <c r="B29" s="182" t="s">
-        <v>337</v>
-      </c>
-      <c r="C29" s="183" t="s">
-        <v>338</v>
-      </c>
-      <c r="D29" s="184" t="n">
+      <c r="A29" s="184" t="s">
+        <v>261</v>
+      </c>
+      <c r="B29" s="184" t="s">
+        <v>302</v>
+      </c>
+      <c r="C29" s="185" t="s">
+        <v>303</v>
+      </c>
+      <c r="D29" s="186" t="n">
         <v>9</v>
       </c>
       <c r="F29" s="10" t="n">
@@ -11496,21 +11394,21 @@
       <c r="H29" s="10" t="n">
         <v>28</v>
       </c>
-      <c r="I29" s="178" t="s">
-        <v>70</v>
+      <c r="I29" s="180" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="44.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="185" t="s">
-        <v>275</v>
-      </c>
-      <c r="B30" s="185" t="s">
-        <v>339</v>
-      </c>
-      <c r="C30" s="186" t="s">
-        <v>340</v>
-      </c>
-      <c r="D30" s="185" t="n">
+      <c r="A30" s="187" t="s">
+        <v>236</v>
+      </c>
+      <c r="B30" s="187" t="s">
+        <v>304</v>
+      </c>
+      <c r="C30" s="188" t="s">
+        <v>305</v>
+      </c>
+      <c r="D30" s="187" t="n">
         <v>10</v>
       </c>
       <c r="F30" s="10"/>
@@ -11520,17 +11418,17 @@
       <c r="H30" s="10" t="n">
         <v>29</v>
       </c>
-      <c r="I30" s="178" t="s">
-        <v>69</v>
+      <c r="I30" s="180" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="185"/>
-      <c r="B31" s="185"/>
-      <c r="C31" s="184" t="s">
-        <v>341</v>
-      </c>
-      <c r="D31" s="184" t="n">
+      <c r="A31" s="187"/>
+      <c r="B31" s="187"/>
+      <c r="C31" s="186" t="s">
+        <v>306</v>
+      </c>
+      <c r="D31" s="186" t="n">
         <v>11</v>
       </c>
       <c r="F31" s="10"/>
@@ -11540,8 +11438,8 @@
       <c r="H31" s="10" t="n">
         <v>30</v>
       </c>
-      <c r="I31" s="176" t="s">
-        <v>62</v>
+      <c r="I31" s="178" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11554,8 +11452,8 @@
       <c r="H32" s="10" t="n">
         <v>31</v>
       </c>
-      <c r="I32" s="176" t="s">
-        <v>62</v>
+      <c r="I32" s="178" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11566,242 +11464,242 @@
       <c r="H33" s="25" t="n">
         <v>32</v>
       </c>
-      <c r="I33" s="187" t="s">
-        <v>70</v>
+      <c r="I33" s="189" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F34" s="188" t="n">
+      <c r="F34" s="190" t="n">
         <v>9</v>
       </c>
-      <c r="G34" s="189" t="s">
-        <v>342</v>
-      </c>
-      <c r="H34" s="190" t="n">
+      <c r="G34" s="191" t="s">
+        <v>307</v>
+      </c>
+      <c r="H34" s="192" t="n">
         <v>33</v>
       </c>
-      <c r="I34" s="189" t="s">
+      <c r="I34" s="191" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F35" s="190"/>
+      <c r="G35" s="191" t="s">
+        <v>308</v>
+      </c>
+      <c r="H35" s="192" t="n">
+        <v>34</v>
+      </c>
+      <c r="I35" s="191" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F36" s="190"/>
+      <c r="G36" s="191" t="s">
+        <v>309</v>
+      </c>
+      <c r="H36" s="192" t="n">
+        <v>35</v>
+      </c>
+      <c r="I36" s="191" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F37" s="190"/>
+      <c r="G37" s="191" t="s">
+        <v>310</v>
+      </c>
+      <c r="H37" s="192" t="n">
+        <v>36</v>
+      </c>
+      <c r="I37" s="191" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F38" s="190"/>
+      <c r="G38" s="191" t="s">
+        <v>311</v>
+      </c>
+      <c r="H38" s="192" t="n">
+        <v>37</v>
+      </c>
+      <c r="I38" s="191" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F39" s="190"/>
+      <c r="G39" s="191" t="s">
+        <v>312</v>
+      </c>
+      <c r="H39" s="192" t="n">
+        <v>38</v>
+      </c>
+      <c r="I39" s="191" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F40" s="190"/>
+      <c r="G40" s="191" t="s">
+        <v>313</v>
+      </c>
+      <c r="H40" s="192" t="n">
+        <v>39</v>
+      </c>
+      <c r="I40" s="191" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F41" s="190"/>
+      <c r="G41" s="191" t="s">
+        <v>314</v>
+      </c>
+      <c r="H41" s="192" t="n">
+        <v>40</v>
+      </c>
+      <c r="I41" s="191" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F35" s="188"/>
-      <c r="G35" s="189" t="s">
-        <v>343</v>
-      </c>
-      <c r="H35" s="190" t="n">
-        <v>34</v>
-      </c>
-      <c r="I35" s="189" t="s">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F42" s="190"/>
+      <c r="G42" s="193" t="s">
+        <v>315</v>
+      </c>
+      <c r="H42" s="194" t="n">
+        <v>41</v>
+      </c>
+      <c r="I42" s="193" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F43" s="195" t="n">
+        <v>10</v>
+      </c>
+      <c r="G43" s="191" t="s">
+        <v>316</v>
+      </c>
+      <c r="H43" s="192" t="n">
+        <v>42</v>
+      </c>
+      <c r="I43" s="191" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F44" s="195"/>
+      <c r="G44" s="191" t="s">
+        <v>317</v>
+      </c>
+      <c r="H44" s="192" t="n">
+        <v>43</v>
+      </c>
+      <c r="I44" s="191" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F45" s="195"/>
+      <c r="G45" s="191" t="s">
+        <v>319</v>
+      </c>
+      <c r="H45" s="192" t="n">
+        <v>44</v>
+      </c>
+      <c r="I45" s="191" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F46" s="195"/>
+      <c r="G46" s="191" t="s">
+        <v>320</v>
+      </c>
+      <c r="H46" s="192" t="n">
+        <v>45</v>
+      </c>
+      <c r="I46" s="191" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F47" s="195"/>
+      <c r="G47" s="191" t="s">
+        <v>321</v>
+      </c>
+      <c r="H47" s="192" t="n">
+        <v>46</v>
+      </c>
+      <c r="I47" s="191" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F48" s="195"/>
+      <c r="G48" s="191" t="s">
+        <v>322</v>
+      </c>
+      <c r="H48" s="192" t="n">
+        <v>47</v>
+      </c>
+      <c r="I48" s="191" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F49" s="195"/>
+      <c r="G49" s="191" t="s">
+        <v>323</v>
+      </c>
+      <c r="H49" s="192" t="n">
+        <v>48</v>
+      </c>
+      <c r="I49" s="191" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F50" s="195" t="n">
+        <v>11</v>
+      </c>
+      <c r="G50" s="191" t="s">
+        <v>324</v>
+      </c>
+      <c r="H50" s="192" t="n">
+        <v>49</v>
+      </c>
+      <c r="I50" s="191" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F36" s="188"/>
-      <c r="G36" s="189" t="s">
-        <v>344</v>
-      </c>
-      <c r="H36" s="190" t="n">
-        <v>35</v>
-      </c>
-      <c r="I36" s="189" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F37" s="188"/>
-      <c r="G37" s="189" t="s">
-        <v>345</v>
-      </c>
-      <c r="H37" s="190" t="n">
-        <v>36</v>
-      </c>
-      <c r="I37" s="189" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F38" s="188"/>
-      <c r="G38" s="189" t="s">
-        <v>346</v>
-      </c>
-      <c r="H38" s="190" t="n">
-        <v>37</v>
-      </c>
-      <c r="I38" s="189" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F39" s="188"/>
-      <c r="G39" s="189" t="s">
-        <v>347</v>
-      </c>
-      <c r="H39" s="190" t="n">
-        <v>38</v>
-      </c>
-      <c r="I39" s="189" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F40" s="188"/>
-      <c r="G40" s="189" t="s">
-        <v>348</v>
-      </c>
-      <c r="H40" s="190" t="n">
-        <v>39</v>
-      </c>
-      <c r="I40" s="189" t="s">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F51" s="195"/>
+      <c r="G51" s="191" t="s">
+        <v>325</v>
+      </c>
+      <c r="H51" s="192" t="n">
+        <v>50</v>
+      </c>
+      <c r="I51" s="191" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F52" s="195"/>
+      <c r="G52" s="191" t="s">
+        <v>326</v>
+      </c>
+      <c r="H52" s="192" t="n">
+        <v>51</v>
+      </c>
+      <c r="I52" s="191" t="s">
         <v>61</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F41" s="188"/>
-      <c r="G41" s="189" t="s">
-        <v>349</v>
-      </c>
-      <c r="H41" s="190" t="n">
-        <v>40</v>
-      </c>
-      <c r="I41" s="189" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F42" s="188"/>
-      <c r="G42" s="191" t="s">
-        <v>350</v>
-      </c>
-      <c r="H42" s="192" t="n">
-        <v>41</v>
-      </c>
-      <c r="I42" s="191" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F43" s="193" t="n">
-        <v>10</v>
-      </c>
-      <c r="G43" s="189" t="s">
-        <v>351</v>
-      </c>
-      <c r="H43" s="190" t="n">
-        <v>42</v>
-      </c>
-      <c r="I43" s="189" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F44" s="193"/>
-      <c r="G44" s="189" t="s">
-        <v>352</v>
-      </c>
-      <c r="H44" s="190" t="n">
-        <v>43</v>
-      </c>
-      <c r="I44" s="189" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F45" s="193"/>
-      <c r="G45" s="189" t="s">
-        <v>354</v>
-      </c>
-      <c r="H45" s="190" t="n">
-        <v>44</v>
-      </c>
-      <c r="I45" s="189" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F46" s="193"/>
-      <c r="G46" s="189" t="s">
-        <v>355</v>
-      </c>
-      <c r="H46" s="190" t="n">
-        <v>45</v>
-      </c>
-      <c r="I46" s="189" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F47" s="193"/>
-      <c r="G47" s="189" t="s">
-        <v>356</v>
-      </c>
-      <c r="H47" s="190" t="n">
-        <v>46</v>
-      </c>
-      <c r="I47" s="189" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F48" s="193"/>
-      <c r="G48" s="189" t="s">
-        <v>357</v>
-      </c>
-      <c r="H48" s="190" t="n">
-        <v>47</v>
-      </c>
-      <c r="I48" s="189" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F49" s="193"/>
-      <c r="G49" s="189" t="s">
-        <v>358</v>
-      </c>
-      <c r="H49" s="190" t="n">
-        <v>48</v>
-      </c>
-      <c r="I49" s="189" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F50" s="193" t="n">
-        <v>11</v>
-      </c>
-      <c r="G50" s="189" t="s">
-        <v>359</v>
-      </c>
-      <c r="H50" s="190" t="n">
-        <v>49</v>
-      </c>
-      <c r="I50" s="189" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F51" s="193"/>
-      <c r="G51" s="189" t="s">
-        <v>360</v>
-      </c>
-      <c r="H51" s="190" t="n">
-        <v>50</v>
-      </c>
-      <c r="I51" s="189" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F52" s="193"/>
-      <c r="G52" s="189" t="s">
-        <v>361</v>
-      </c>
-      <c r="H52" s="190" t="n">
-        <v>51</v>
-      </c>
-      <c r="I52" s="189" t="s">
-        <v>62</v>
       </c>
     </row>
   </sheetData>
